--- a/24_DS_CLUB_BATCH1_AHM/Attendance.xlsx
+++ b/24_DS_CLUB_BATCH1_AHM/Attendance.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\Batches\24_DS_CLUB_BATCH1_AHM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_CLUB_BATCH1_AHM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E23871-6BB6-40F1-B5AF-BA2B4ECE549C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{959F573E-091A-4FA6-823B-5190A5688702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
   <sheets>
     <sheet name="Attendance" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="25">
   <si>
     <t>Name</t>
   </si>
@@ -94,6 +95,12 @@
   </si>
   <si>
     <t>Adwait Kathiriya</t>
+  </si>
+  <si>
+    <t>Total/80</t>
+  </si>
+  <si>
+    <t>Total/5</t>
   </si>
 </sst>
 </file>
@@ -1357,4 +1364,1232 @@
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4823A201-E521-4A8B-9AE3-2FAFD3CCE230}">
+  <dimension ref="A1:S16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>45424</v>
+      </c>
+      <c r="C1" s="1">
+        <v>45431</v>
+      </c>
+      <c r="D1" s="1">
+        <v>45438</v>
+      </c>
+      <c r="E1" s="1">
+        <v>45445</v>
+      </c>
+      <c r="F1" s="1">
+        <v>45459</v>
+      </c>
+      <c r="G1" s="1">
+        <v>45466</v>
+      </c>
+      <c r="H1" s="1">
+        <v>45473</v>
+      </c>
+      <c r="I1" s="1">
+        <v>45487</v>
+      </c>
+      <c r="J1" s="1">
+        <v>45494</v>
+      </c>
+      <c r="K1" s="1">
+        <v>45522</v>
+      </c>
+      <c r="L1" s="1">
+        <v>45529</v>
+      </c>
+      <c r="M1" s="1">
+        <v>45536</v>
+      </c>
+      <c r="N1" s="1">
+        <v>45543</v>
+      </c>
+      <c r="O1" s="1">
+        <v>45550</v>
+      </c>
+      <c r="P1" s="1">
+        <v>45557</v>
+      </c>
+      <c r="Q1" s="1">
+        <v>45578</v>
+      </c>
+      <c r="R1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2">
+        <f>_xlfn.IFS(Attendance!C2="P",5,Attendance!C2="O",3,Attendance!C2="A",0,Attendance!C2="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <f>_xlfn.IFS(Attendance!D2="P",5,Attendance!D2="O",3,Attendance!D2="A",0,Attendance!D2="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <f>_xlfn.IFS(Attendance!E2="P",5,Attendance!E2="O",3,Attendance!E2="A",0,Attendance!E2="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <f>_xlfn.IFS(Attendance!F2="P",5,Attendance!F2="O",3,Attendance!F2="A",0,Attendance!F2="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <f>_xlfn.IFS(Attendance!G2="P",5,Attendance!G2="O",3,Attendance!G2="A",0,Attendance!G2="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <f>_xlfn.IFS(Attendance!H2="P",5,Attendance!H2="O",3,Attendance!H2="A",0,Attendance!H2="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <f>_xlfn.IFS(Attendance!I2="P",5,Attendance!I2="O",3,Attendance!I2="A",0,Attendance!I2="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <f>_xlfn.IFS(Attendance!J2="P",5,Attendance!J2="O",3,Attendance!J2="A",0,Attendance!J2="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <f>_xlfn.IFS(Attendance!K2="P",5,Attendance!K2="O",3,Attendance!K2="A",0,Attendance!K2="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <f>_xlfn.IFS(Attendance!L2="P",5,Attendance!L2="O",3,Attendance!L2="A",0,Attendance!L2="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <f>_xlfn.IFS(Attendance!M2="P",5,Attendance!M2="O",3,Attendance!M2="A",0,Attendance!M2="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <f>_xlfn.IFS(Attendance!N2="P",5,Attendance!N2="O",3,Attendance!N2="A",0,Attendance!N2="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="N2">
+        <f>_xlfn.IFS(Attendance!O2="P",5,Attendance!O2="O",3,Attendance!O2="A",0,Attendance!O2="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="O2">
+        <f>_xlfn.IFS(Attendance!P2="P",5,Attendance!P2="O",3,Attendance!P2="A",0,Attendance!P2="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="P2">
+        <f>_xlfn.IFS(Attendance!Q2="P",5,Attendance!Q2="O",3,Attendance!Q2="A",0,Attendance!Q2="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="Q2">
+        <f>_xlfn.IFS(Attendance!R2="P",5,Attendance!R2="O",3,Attendance!R2="A",0,Attendance!R2="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <f>SUM(B2:Q2)</f>
+        <v>21</v>
+      </c>
+      <c r="S2">
+        <f>ROUND(R2*5/80, 2)</f>
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3">
+        <f>_xlfn.IFS(Attendance!C3="P",5,Attendance!C3="O",3,Attendance!C3="A",0,Attendance!C3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <f>_xlfn.IFS(Attendance!D3="P",5,Attendance!D3="O",3,Attendance!D3="A",0,Attendance!D3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <f>_xlfn.IFS(Attendance!E3="P",5,Attendance!E3="O",3,Attendance!E3="A",0,Attendance!E3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <f>_xlfn.IFS(Attendance!F3="P",5,Attendance!F3="O",3,Attendance!F3="A",0,Attendance!F3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <f>_xlfn.IFS(Attendance!G3="P",5,Attendance!G3="O",3,Attendance!G3="A",0,Attendance!G3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <f>_xlfn.IFS(Attendance!H3="P",5,Attendance!H3="O",3,Attendance!H3="A",0,Attendance!H3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <f>_xlfn.IFS(Attendance!I3="P",5,Attendance!I3="O",3,Attendance!I3="A",0,Attendance!I3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <f>_xlfn.IFS(Attendance!J3="P",5,Attendance!J3="O",3,Attendance!J3="A",0,Attendance!J3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <f>_xlfn.IFS(Attendance!K3="P",5,Attendance!K3="O",3,Attendance!K3="A",0,Attendance!K3="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <f>_xlfn.IFS(Attendance!L3="P",5,Attendance!L3="O",3,Attendance!L3="A",0,Attendance!L3="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <f>_xlfn.IFS(Attendance!M3="P",5,Attendance!M3="O",3,Attendance!M3="A",0,Attendance!M3="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <f>_xlfn.IFS(Attendance!N3="P",5,Attendance!N3="O",3,Attendance!N3="A",0,Attendance!N3="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="N3">
+        <f>_xlfn.IFS(Attendance!O3="P",5,Attendance!O3="O",3,Attendance!O3="A",0,Attendance!O3="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="O3">
+        <f>_xlfn.IFS(Attendance!P3="P",5,Attendance!P3="O",3,Attendance!P3="A",0,Attendance!P3="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="P3">
+        <f>_xlfn.IFS(Attendance!Q3="P",5,Attendance!Q3="O",3,Attendance!Q3="A",0,Attendance!Q3="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="Q3">
+        <f>_xlfn.IFS(Attendance!R3="P",5,Attendance!R3="O",3,Attendance!R3="A",0,Attendance!R3="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R16" si="0">SUM(B3:Q3)</f>
+        <v>32</v>
+      </c>
+      <c r="S3">
+        <f t="shared" ref="S3:S16" si="1">ROUND(R3*5/80, 2)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4">
+        <f>_xlfn.IFS(Attendance!C4="P",5,Attendance!C4="O",3,Attendance!C4="A",0,Attendance!C4="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <f>_xlfn.IFS(Attendance!D4="P",5,Attendance!D4="O",3,Attendance!D4="A",0,Attendance!D4="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <f>_xlfn.IFS(Attendance!E4="P",5,Attendance!E4="O",3,Attendance!E4="A",0,Attendance!E4="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <f>_xlfn.IFS(Attendance!F4="P",5,Attendance!F4="O",3,Attendance!F4="A",0,Attendance!F4="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <f>_xlfn.IFS(Attendance!G4="P",5,Attendance!G4="O",3,Attendance!G4="A",0,Attendance!G4="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <f>_xlfn.IFS(Attendance!H4="P",5,Attendance!H4="O",3,Attendance!H4="A",0,Attendance!H4="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <f>_xlfn.IFS(Attendance!I4="P",5,Attendance!I4="O",3,Attendance!I4="A",0,Attendance!I4="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <f>_xlfn.IFS(Attendance!J4="P",5,Attendance!J4="O",3,Attendance!J4="A",0,Attendance!J4="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <f>_xlfn.IFS(Attendance!K4="P",5,Attendance!K4="O",3,Attendance!K4="A",0,Attendance!K4="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <f>_xlfn.IFS(Attendance!L4="P",5,Attendance!L4="O",3,Attendance!L4="A",0,Attendance!L4="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <f>_xlfn.IFS(Attendance!M4="P",5,Attendance!M4="O",3,Attendance!M4="A",0,Attendance!M4="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <f>_xlfn.IFS(Attendance!N4="P",5,Attendance!N4="O",3,Attendance!N4="A",0,Attendance!N4="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="N4">
+        <f>_xlfn.IFS(Attendance!O4="P",5,Attendance!O4="O",3,Attendance!O4="A",0,Attendance!O4="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="O4">
+        <f>_xlfn.IFS(Attendance!P4="P",5,Attendance!P4="O",3,Attendance!P4="A",0,Attendance!P4="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="P4">
+        <f>_xlfn.IFS(Attendance!Q4="P",5,Attendance!Q4="O",3,Attendance!Q4="A",0,Attendance!Q4="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="Q4">
+        <f>_xlfn.IFS(Attendance!R4="P",5,Attendance!R4="O",3,Attendance!R4="A",0,Attendance!R4="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="S4">
+        <f t="shared" si="1"/>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5">
+        <f>_xlfn.IFS(Attendance!C5="P",5,Attendance!C5="O",3,Attendance!C5="A",0,Attendance!C5="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <f>_xlfn.IFS(Attendance!D5="P",5,Attendance!D5="O",3,Attendance!D5="A",0,Attendance!D5="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <f>_xlfn.IFS(Attendance!E5="P",5,Attendance!E5="O",3,Attendance!E5="A",0,Attendance!E5="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <f>_xlfn.IFS(Attendance!F5="P",5,Attendance!F5="O",3,Attendance!F5="A",0,Attendance!F5="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <f>_xlfn.IFS(Attendance!G5="P",5,Attendance!G5="O",3,Attendance!G5="A",0,Attendance!G5="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <f>_xlfn.IFS(Attendance!H5="P",5,Attendance!H5="O",3,Attendance!H5="A",0,Attendance!H5="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <f>_xlfn.IFS(Attendance!I5="P",5,Attendance!I5="O",3,Attendance!I5="A",0,Attendance!I5="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <f>_xlfn.IFS(Attendance!J5="P",5,Attendance!J5="O",3,Attendance!J5="A",0,Attendance!J5="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <f>_xlfn.IFS(Attendance!K5="P",5,Attendance!K5="O",3,Attendance!K5="A",0,Attendance!K5="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <f>_xlfn.IFS(Attendance!L5="P",5,Attendance!L5="O",3,Attendance!L5="A",0,Attendance!L5="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="L5">
+        <f>_xlfn.IFS(Attendance!M5="P",5,Attendance!M5="O",3,Attendance!M5="A",0,Attendance!M5="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <f>_xlfn.IFS(Attendance!N5="P",5,Attendance!N5="O",3,Attendance!N5="A",0,Attendance!N5="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="N5">
+        <f>_xlfn.IFS(Attendance!O5="P",5,Attendance!O5="O",3,Attendance!O5="A",0,Attendance!O5="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="O5">
+        <f>_xlfn.IFS(Attendance!P5="P",5,Attendance!P5="O",3,Attendance!P5="A",0,Attendance!P5="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="P5">
+        <f>_xlfn.IFS(Attendance!Q5="P",5,Attendance!Q5="O",3,Attendance!Q5="A",0,Attendance!Q5="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="Q5">
+        <f>_xlfn.IFS(Attendance!R5="P",5,Attendance!R5="O",3,Attendance!R5="A",0,Attendance!R5="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <f>_xlfn.IFS(Attendance!C6="P",5,Attendance!C6="O",3,Attendance!C6="A",0,Attendance!C6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <f>_xlfn.IFS(Attendance!D6="P",5,Attendance!D6="O",3,Attendance!D6="A",0,Attendance!D6="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <f>_xlfn.IFS(Attendance!E6="P",5,Attendance!E6="O",3,Attendance!E6="A",0,Attendance!E6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <f>_xlfn.IFS(Attendance!F6="P",5,Attendance!F6="O",3,Attendance!F6="A",0,Attendance!F6="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <f>_xlfn.IFS(Attendance!G6="P",5,Attendance!G6="O",3,Attendance!G6="A",0,Attendance!G6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <f>_xlfn.IFS(Attendance!H6="P",5,Attendance!H6="O",3,Attendance!H6="A",0,Attendance!H6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <f>_xlfn.IFS(Attendance!I6="P",5,Attendance!I6="O",3,Attendance!I6="A",0,Attendance!I6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <f>_xlfn.IFS(Attendance!J6="P",5,Attendance!J6="O",3,Attendance!J6="A",0,Attendance!J6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <f>_xlfn.IFS(Attendance!K6="P",5,Attendance!K6="O",3,Attendance!K6="A",0,Attendance!K6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <f>_xlfn.IFS(Attendance!L6="P",5,Attendance!L6="O",3,Attendance!L6="A",0,Attendance!L6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <f>_xlfn.IFS(Attendance!M6="P",5,Attendance!M6="O",3,Attendance!M6="A",0,Attendance!M6="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <f>_xlfn.IFS(Attendance!N6="P",5,Attendance!N6="O",3,Attendance!N6="A",0,Attendance!N6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="N6">
+        <f>_xlfn.IFS(Attendance!O6="P",5,Attendance!O6="O",3,Attendance!O6="A",0,Attendance!O6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="O6">
+        <f>_xlfn.IFS(Attendance!P6="P",5,Attendance!P6="O",3,Attendance!P6="A",0,Attendance!P6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="P6">
+        <f>_xlfn.IFS(Attendance!Q6="P",5,Attendance!Q6="O",3,Attendance!Q6="A",0,Attendance!Q6="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="Q6">
+        <f>_xlfn.IFS(Attendance!R6="P",5,Attendance!R6="O",3,Attendance!R6="A",0,Attendance!R6="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <f>_xlfn.IFS(Attendance!C7="P",5,Attendance!C7="O",3,Attendance!C7="A",0,Attendance!C7="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <f>_xlfn.IFS(Attendance!D7="P",5,Attendance!D7="O",3,Attendance!D7="A",0,Attendance!D7="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <f>_xlfn.IFS(Attendance!E7="P",5,Attendance!E7="O",3,Attendance!E7="A",0,Attendance!E7="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <f>_xlfn.IFS(Attendance!F7="P",5,Attendance!F7="O",3,Attendance!F7="A",0,Attendance!F7="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <f>_xlfn.IFS(Attendance!G7="P",5,Attendance!G7="O",3,Attendance!G7="A",0,Attendance!G7="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <f>_xlfn.IFS(Attendance!H7="P",5,Attendance!H7="O",3,Attendance!H7="A",0,Attendance!H7="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <f>_xlfn.IFS(Attendance!I7="P",5,Attendance!I7="O",3,Attendance!I7="A",0,Attendance!I7="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <f>_xlfn.IFS(Attendance!J7="P",5,Attendance!J7="O",3,Attendance!J7="A",0,Attendance!J7="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <f>_xlfn.IFS(Attendance!K7="P",5,Attendance!K7="O",3,Attendance!K7="A",0,Attendance!K7="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="K7">
+        <f>_xlfn.IFS(Attendance!L7="P",5,Attendance!L7="O",3,Attendance!L7="A",0,Attendance!L7="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="L7">
+        <f>_xlfn.IFS(Attendance!M7="P",5,Attendance!M7="O",3,Attendance!M7="A",0,Attendance!M7="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="M7">
+        <f>_xlfn.IFS(Attendance!N7="P",5,Attendance!N7="O",3,Attendance!N7="A",0,Attendance!N7="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="N7">
+        <f>_xlfn.IFS(Attendance!O7="P",5,Attendance!O7="O",3,Attendance!O7="A",0,Attendance!O7="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="O7">
+        <f>_xlfn.IFS(Attendance!P7="P",5,Attendance!P7="O",3,Attendance!P7="A",0,Attendance!P7="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="P7">
+        <f>_xlfn.IFS(Attendance!Q7="P",5,Attendance!Q7="O",3,Attendance!Q7="A",0,Attendance!Q7="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="Q7">
+        <f>_xlfn.IFS(Attendance!R7="P",5,Attendance!R7="O",3,Attendance!R7="A",0,Attendance!R7="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="1"/>
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <f>_xlfn.IFS(Attendance!C8="P",5,Attendance!C8="O",3,Attendance!C8="A",0,Attendance!C8="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <f>_xlfn.IFS(Attendance!D8="P",5,Attendance!D8="O",3,Attendance!D8="A",0,Attendance!D8="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <f>_xlfn.IFS(Attendance!E8="P",5,Attendance!E8="O",3,Attendance!E8="A",0,Attendance!E8="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <f>_xlfn.IFS(Attendance!F8="P",5,Attendance!F8="O",3,Attendance!F8="A",0,Attendance!F8="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="F8">
+        <f>_xlfn.IFS(Attendance!G8="P",5,Attendance!G8="O",3,Attendance!G8="A",0,Attendance!G8="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="G8">
+        <f>_xlfn.IFS(Attendance!H8="P",5,Attendance!H8="O",3,Attendance!H8="A",0,Attendance!H8="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="H8">
+        <f>_xlfn.IFS(Attendance!I8="P",5,Attendance!I8="O",3,Attendance!I8="A",0,Attendance!I8="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <f>_xlfn.IFS(Attendance!J8="P",5,Attendance!J8="O",3,Attendance!J8="A",0,Attendance!J8="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="J8">
+        <f>_xlfn.IFS(Attendance!K8="P",5,Attendance!K8="O",3,Attendance!K8="A",0,Attendance!K8="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="K8">
+        <f>_xlfn.IFS(Attendance!L8="P",5,Attendance!L8="O",3,Attendance!L8="A",0,Attendance!L8="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="L8">
+        <f>_xlfn.IFS(Attendance!M8="P",5,Attendance!M8="O",3,Attendance!M8="A",0,Attendance!M8="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="M8">
+        <f>_xlfn.IFS(Attendance!N8="P",5,Attendance!N8="O",3,Attendance!N8="A",0,Attendance!N8="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="N8">
+        <f>_xlfn.IFS(Attendance!O8="P",5,Attendance!O8="O",3,Attendance!O8="A",0,Attendance!O8="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="O8">
+        <f>_xlfn.IFS(Attendance!P8="P",5,Attendance!P8="O",3,Attendance!P8="A",0,Attendance!P8="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <f>_xlfn.IFS(Attendance!Q8="P",5,Attendance!Q8="O",3,Attendance!Q8="A",0,Attendance!Q8="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <f>_xlfn.IFS(Attendance!R8="P",5,Attendance!R8="O",3,Attendance!R8="A",0,Attendance!R8="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="1"/>
+        <v>2.56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <f>_xlfn.IFS(Attendance!C9="P",5,Attendance!C9="O",3,Attendance!C9="A",0,Attendance!C9="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <f>_xlfn.IFS(Attendance!D9="P",5,Attendance!D9="O",3,Attendance!D9="A",0,Attendance!D9="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <f>_xlfn.IFS(Attendance!E9="P",5,Attendance!E9="O",3,Attendance!E9="A",0,Attendance!E9="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <f>_xlfn.IFS(Attendance!F9="P",5,Attendance!F9="O",3,Attendance!F9="A",0,Attendance!F9="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="F9">
+        <f>_xlfn.IFS(Attendance!G9="P",5,Attendance!G9="O",3,Attendance!G9="A",0,Attendance!G9="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <f>_xlfn.IFS(Attendance!H9="P",5,Attendance!H9="O",3,Attendance!H9="A",0,Attendance!H9="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <f>_xlfn.IFS(Attendance!I9="P",5,Attendance!I9="O",3,Attendance!I9="A",0,Attendance!I9="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <f>_xlfn.IFS(Attendance!J9="P",5,Attendance!J9="O",3,Attendance!J9="A",0,Attendance!J9="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <f>_xlfn.IFS(Attendance!K9="P",5,Attendance!K9="O",3,Attendance!K9="A",0,Attendance!K9="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <f>_xlfn.IFS(Attendance!L9="P",5,Attendance!L9="O",3,Attendance!L9="A",0,Attendance!L9="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <f>_xlfn.IFS(Attendance!M9="P",5,Attendance!M9="O",3,Attendance!M9="A",0,Attendance!M9="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <f>_xlfn.IFS(Attendance!N9="P",5,Attendance!N9="O",3,Attendance!N9="A",0,Attendance!N9="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <f>_xlfn.IFS(Attendance!O9="P",5,Attendance!O9="O",3,Attendance!O9="A",0,Attendance!O9="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <f>_xlfn.IFS(Attendance!P9="P",5,Attendance!P9="O",3,Attendance!P9="A",0,Attendance!P9="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <f>_xlfn.IFS(Attendance!Q9="P",5,Attendance!Q9="O",3,Attendance!Q9="A",0,Attendance!Q9="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <f>_xlfn.IFS(Attendance!R9="P",5,Attendance!R9="O",3,Attendance!R9="A",0,Attendance!R9="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="1"/>
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10">
+        <f>_xlfn.IFS(Attendance!C10="P",5,Attendance!C10="O",3,Attendance!C10="A",0,Attendance!C10="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <f>_xlfn.IFS(Attendance!D10="P",5,Attendance!D10="O",3,Attendance!D10="A",0,Attendance!D10="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <f>_xlfn.IFS(Attendance!E10="P",5,Attendance!E10="O",3,Attendance!E10="A",0,Attendance!E10="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <f>_xlfn.IFS(Attendance!F10="P",5,Attendance!F10="O",3,Attendance!F10="A",0,Attendance!F10="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <f>_xlfn.IFS(Attendance!G10="P",5,Attendance!G10="O",3,Attendance!G10="A",0,Attendance!G10="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <f>_xlfn.IFS(Attendance!H10="P",5,Attendance!H10="O",3,Attendance!H10="A",0,Attendance!H10="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <f>_xlfn.IFS(Attendance!I10="P",5,Attendance!I10="O",3,Attendance!I10="A",0,Attendance!I10="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <f>_xlfn.IFS(Attendance!J10="P",5,Attendance!J10="O",3,Attendance!J10="A",0,Attendance!J10="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="J10">
+        <f>_xlfn.IFS(Attendance!K10="P",5,Attendance!K10="O",3,Attendance!K10="A",0,Attendance!K10="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="K10">
+        <f>_xlfn.IFS(Attendance!L10="P",5,Attendance!L10="O",3,Attendance!L10="A",0,Attendance!L10="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="L10">
+        <f>_xlfn.IFS(Attendance!M10="P",5,Attendance!M10="O",3,Attendance!M10="A",0,Attendance!M10="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="M10">
+        <f>_xlfn.IFS(Attendance!N10="P",5,Attendance!N10="O",3,Attendance!N10="A",0,Attendance!N10="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="N10">
+        <f>_xlfn.IFS(Attendance!O10="P",5,Attendance!O10="O",3,Attendance!O10="A",0,Attendance!O10="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <f>_xlfn.IFS(Attendance!P10="P",5,Attendance!P10="O",3,Attendance!P10="A",0,Attendance!P10="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <f>_xlfn.IFS(Attendance!Q10="P",5,Attendance!Q10="O",3,Attendance!Q10="A",0,Attendance!Q10="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <f>_xlfn.IFS(Attendance!R10="P",5,Attendance!R10="O",3,Attendance!R10="A",0,Attendance!R10="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="1"/>
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11">
+        <f>_xlfn.IFS(Attendance!C11="P",5,Attendance!C11="O",3,Attendance!C11="A",0,Attendance!C11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <f>_xlfn.IFS(Attendance!D11="P",5,Attendance!D11="O",3,Attendance!D11="A",0,Attendance!D11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <f>_xlfn.IFS(Attendance!E11="P",5,Attendance!E11="O",3,Attendance!E11="A",0,Attendance!E11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <f>_xlfn.IFS(Attendance!F11="P",5,Attendance!F11="O",3,Attendance!F11="A",0,Attendance!F11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <f>_xlfn.IFS(Attendance!G11="P",5,Attendance!G11="O",3,Attendance!G11="A",0,Attendance!G11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <f>_xlfn.IFS(Attendance!H11="P",5,Attendance!H11="O",3,Attendance!H11="A",0,Attendance!H11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <f>_xlfn.IFS(Attendance!I11="P",5,Attendance!I11="O",3,Attendance!I11="A",0,Attendance!I11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <f>_xlfn.IFS(Attendance!J11="P",5,Attendance!J11="O",3,Attendance!J11="A",0,Attendance!J11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <f>_xlfn.IFS(Attendance!K11="P",5,Attendance!K11="O",3,Attendance!K11="A",0,Attendance!K11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <f>_xlfn.IFS(Attendance!L11="P",5,Attendance!L11="O",3,Attendance!L11="A",0,Attendance!L11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <f>_xlfn.IFS(Attendance!M11="P",5,Attendance!M11="O",3,Attendance!M11="A",0,Attendance!M11="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="M11">
+        <f>_xlfn.IFS(Attendance!N11="P",5,Attendance!N11="O",3,Attendance!N11="A",0,Attendance!N11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <f>_xlfn.IFS(Attendance!O11="P",5,Attendance!O11="O",3,Attendance!O11="A",0,Attendance!O11="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="O11">
+        <f>_xlfn.IFS(Attendance!P11="P",5,Attendance!P11="O",3,Attendance!P11="A",0,Attendance!P11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <f>_xlfn.IFS(Attendance!Q11="P",5,Attendance!Q11="O",3,Attendance!Q11="A",0,Attendance!Q11="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="Q11">
+        <f>_xlfn.IFS(Attendance!R11="P",5,Attendance!R11="O",3,Attendance!R11="A",0,Attendance!R11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="1"/>
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <f>_xlfn.IFS(Attendance!C12="P",5,Attendance!C12="O",3,Attendance!C12="A",0,Attendance!C12="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <f>_xlfn.IFS(Attendance!D12="P",5,Attendance!D12="O",3,Attendance!D12="A",0,Attendance!D12="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="D12">
+        <f>_xlfn.IFS(Attendance!E12="P",5,Attendance!E12="O",3,Attendance!E12="A",0,Attendance!E12="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="E12">
+        <f>_xlfn.IFS(Attendance!F12="P",5,Attendance!F12="O",3,Attendance!F12="A",0,Attendance!F12="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="F12">
+        <f>_xlfn.IFS(Attendance!G12="P",5,Attendance!G12="O",3,Attendance!G12="A",0,Attendance!G12="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <f>_xlfn.IFS(Attendance!H12="P",5,Attendance!H12="O",3,Attendance!H12="A",0,Attendance!H12="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H12">
+        <f>_xlfn.IFS(Attendance!I12="P",5,Attendance!I12="O",3,Attendance!I12="A",0,Attendance!I12="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <f>_xlfn.IFS(Attendance!J12="P",5,Attendance!J12="O",3,Attendance!J12="A",0,Attendance!J12="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <f>_xlfn.IFS(Attendance!K12="P",5,Attendance!K12="O",3,Attendance!K12="A",0,Attendance!K12="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <f>_xlfn.IFS(Attendance!L12="P",5,Attendance!L12="O",3,Attendance!L12="A",0,Attendance!L12="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <f>_xlfn.IFS(Attendance!M12="P",5,Attendance!M12="O",3,Attendance!M12="A",0,Attendance!M12="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <f>_xlfn.IFS(Attendance!N12="P",5,Attendance!N12="O",3,Attendance!N12="A",0,Attendance!N12="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <f>_xlfn.IFS(Attendance!O12="P",5,Attendance!O12="O",3,Attendance!O12="A",0,Attendance!O12="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <f>_xlfn.IFS(Attendance!P12="P",5,Attendance!P12="O",3,Attendance!P12="A",0,Attendance!P12="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <f>_xlfn.IFS(Attendance!Q12="P",5,Attendance!Q12="O",3,Attendance!Q12="A",0,Attendance!Q12="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <f>_xlfn.IFS(Attendance!R12="P",5,Attendance!R12="O",3,Attendance!R12="A",0,Attendance!R12="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="1"/>
+        <v>1.1299999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13">
+        <f>_xlfn.IFS(Attendance!C13="P",5,Attendance!C13="O",3,Attendance!C13="A",0,Attendance!C13="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <f>_xlfn.IFS(Attendance!D13="P",5,Attendance!D13="O",3,Attendance!D13="A",0,Attendance!D13="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="D13">
+        <f>_xlfn.IFS(Attendance!E13="P",5,Attendance!E13="O",3,Attendance!E13="A",0,Attendance!E13="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="E13">
+        <f>_xlfn.IFS(Attendance!F13="P",5,Attendance!F13="O",3,Attendance!F13="A",0,Attendance!F13="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <f>_xlfn.IFS(Attendance!G13="P",5,Attendance!G13="O",3,Attendance!G13="A",0,Attendance!G13="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <f>_xlfn.IFS(Attendance!H13="P",5,Attendance!H13="O",3,Attendance!H13="A",0,Attendance!H13="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <f>_xlfn.IFS(Attendance!I13="P",5,Attendance!I13="O",3,Attendance!I13="A",0,Attendance!I13="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <f>_xlfn.IFS(Attendance!J13="P",5,Attendance!J13="O",3,Attendance!J13="A",0,Attendance!J13="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <f>_xlfn.IFS(Attendance!K13="P",5,Attendance!K13="O",3,Attendance!K13="A",0,Attendance!K13="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <f>_xlfn.IFS(Attendance!L13="P",5,Attendance!L13="O",3,Attendance!L13="A",0,Attendance!L13="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <f>_xlfn.IFS(Attendance!M13="P",5,Attendance!M13="O",3,Attendance!M13="A",0,Attendance!M13="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <f>_xlfn.IFS(Attendance!N13="P",5,Attendance!N13="O",3,Attendance!N13="A",0,Attendance!N13="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <f>_xlfn.IFS(Attendance!O13="P",5,Attendance!O13="O",3,Attendance!O13="A",0,Attendance!O13="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <f>_xlfn.IFS(Attendance!P13="P",5,Attendance!P13="O",3,Attendance!P13="A",0,Attendance!P13="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <f>_xlfn.IFS(Attendance!Q13="P",5,Attendance!Q13="O",3,Attendance!Q13="A",0,Attendance!Q13="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <f>_xlfn.IFS(Attendance!R13="P",5,Attendance!R13="O",3,Attendance!R13="A",0,Attendance!R13="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="1"/>
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14">
+        <f>_xlfn.IFS(Attendance!C14="P",5,Attendance!C14="O",3,Attendance!C14="A",0,Attendance!C14="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <f>_xlfn.IFS(Attendance!D14="P",5,Attendance!D14="O",3,Attendance!D14="A",0,Attendance!D14="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <f>_xlfn.IFS(Attendance!E14="P",5,Attendance!E14="O",3,Attendance!E14="A",0,Attendance!E14="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <f>_xlfn.IFS(Attendance!F14="P",5,Attendance!F14="O",3,Attendance!F14="A",0,Attendance!F14="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="F14">
+        <f>_xlfn.IFS(Attendance!G14="P",5,Attendance!G14="O",3,Attendance!G14="A",0,Attendance!G14="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <f>_xlfn.IFS(Attendance!H14="P",5,Attendance!H14="O",3,Attendance!H14="A",0,Attendance!H14="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <f>_xlfn.IFS(Attendance!I14="P",5,Attendance!I14="O",3,Attendance!I14="A",0,Attendance!I14="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I14">
+        <f>_xlfn.IFS(Attendance!J14="P",5,Attendance!J14="O",3,Attendance!J14="A",0,Attendance!J14="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <f>_xlfn.IFS(Attendance!K14="P",5,Attendance!K14="O",3,Attendance!K14="A",0,Attendance!K14="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="K14">
+        <f>_xlfn.IFS(Attendance!L14="P",5,Attendance!L14="O",3,Attendance!L14="A",0,Attendance!L14="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="L14">
+        <f>_xlfn.IFS(Attendance!M14="P",5,Attendance!M14="O",3,Attendance!M14="A",0,Attendance!M14="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="M14">
+        <f>_xlfn.IFS(Attendance!N14="P",5,Attendance!N14="O",3,Attendance!N14="A",0,Attendance!N14="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="N14">
+        <f>_xlfn.IFS(Attendance!O14="P",5,Attendance!O14="O",3,Attendance!O14="A",0,Attendance!O14="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="O14">
+        <f>_xlfn.IFS(Attendance!P14="P",5,Attendance!P14="O",3,Attendance!P14="A",0,Attendance!P14="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <f>_xlfn.IFS(Attendance!Q14="P",5,Attendance!Q14="O",3,Attendance!Q14="A",0,Attendance!Q14="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <f>_xlfn.IFS(Attendance!R14="P",5,Attendance!R14="O",3,Attendance!R14="A",0,Attendance!R14="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="1"/>
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15">
+        <f>_xlfn.IFS(Attendance!C15="P",5,Attendance!C15="O",3,Attendance!C15="A",0,Attendance!C15="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <f>_xlfn.IFS(Attendance!D15="P",5,Attendance!D15="O",3,Attendance!D15="A",0,Attendance!D15="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <f>_xlfn.IFS(Attendance!E15="P",5,Attendance!E15="O",3,Attendance!E15="A",0,Attendance!E15="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <f>_xlfn.IFS(Attendance!F15="P",5,Attendance!F15="O",3,Attendance!F15="A",0,Attendance!F15="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <f>_xlfn.IFS(Attendance!G15="P",5,Attendance!G15="O",3,Attendance!G15="A",0,Attendance!G15="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <f>_xlfn.IFS(Attendance!H15="P",5,Attendance!H15="O",3,Attendance!H15="A",0,Attendance!H15="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <f>_xlfn.IFS(Attendance!I15="P",5,Attendance!I15="O",3,Attendance!I15="A",0,Attendance!I15="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <f>_xlfn.IFS(Attendance!J15="P",5,Attendance!J15="O",3,Attendance!J15="A",0,Attendance!J15="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <f>_xlfn.IFS(Attendance!K15="P",5,Attendance!K15="O",3,Attendance!K15="A",0,Attendance!K15="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <f>_xlfn.IFS(Attendance!L15="P",5,Attendance!L15="O",3,Attendance!L15="A",0,Attendance!L15="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <f>_xlfn.IFS(Attendance!M15="P",5,Attendance!M15="O",3,Attendance!M15="A",0,Attendance!M15="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <f>_xlfn.IFS(Attendance!N15="P",5,Attendance!N15="O",3,Attendance!N15="A",0,Attendance!N15="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <f>_xlfn.IFS(Attendance!O15="P",5,Attendance!O15="O",3,Attendance!O15="A",0,Attendance!O15="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <f>_xlfn.IFS(Attendance!P15="P",5,Attendance!P15="O",3,Attendance!P15="A",0,Attendance!P15="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <f>_xlfn.IFS(Attendance!Q15="P",5,Attendance!Q15="O",3,Attendance!Q15="A",0,Attendance!Q15="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <f>_xlfn.IFS(Attendance!R15="P",5,Attendance!R15="O",3,Attendance!R15="A",0,Attendance!R15="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16">
+        <f>_xlfn.IFS(Attendance!C16="P",5,Attendance!C16="O",3,Attendance!C16="A",0,Attendance!C16="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <f>_xlfn.IFS(Attendance!D16="P",5,Attendance!D16="O",3,Attendance!D16="A",0,Attendance!D16="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <f>_xlfn.IFS(Attendance!E16="P",5,Attendance!E16="O",3,Attendance!E16="A",0,Attendance!E16="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <f>_xlfn.IFS(Attendance!F16="P",5,Attendance!F16="O",3,Attendance!F16="A",0,Attendance!F16="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <f>_xlfn.IFS(Attendance!G16="P",5,Attendance!G16="O",3,Attendance!G16="A",0,Attendance!G16="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <f>_xlfn.IFS(Attendance!H16="P",5,Attendance!H16="O",3,Attendance!H16="A",0,Attendance!H16="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <f>_xlfn.IFS(Attendance!I16="P",5,Attendance!I16="O",3,Attendance!I16="A",0,Attendance!I16="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <f>_xlfn.IFS(Attendance!J16="P",5,Attendance!J16="O",3,Attendance!J16="A",0,Attendance!J16="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <f>_xlfn.IFS(Attendance!K16="P",5,Attendance!K16="O",3,Attendance!K16="A",0,Attendance!K16="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <f>_xlfn.IFS(Attendance!L16="P",5,Attendance!L16="O",3,Attendance!L16="A",0,Attendance!L16="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <f>_xlfn.IFS(Attendance!M16="P",5,Attendance!M16="O",3,Attendance!M16="A",0,Attendance!M16="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <f>_xlfn.IFS(Attendance!N16="P",5,Attendance!N16="O",3,Attendance!N16="A",0,Attendance!N16="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <f>_xlfn.IFS(Attendance!O16="P",5,Attendance!O16="O",3,Attendance!O16="A",0,Attendance!O16="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <f>_xlfn.IFS(Attendance!P16="P",5,Attendance!P16="O",3,Attendance!P16="A",0,Attendance!P16="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <f>_xlfn.IFS(Attendance!Q16="P",5,Attendance!Q16="O",3,Attendance!Q16="A",0,Attendance!Q16="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <f>_xlfn.IFS(Attendance!R16="P",5,Attendance!R16="O",3,Attendance!R16="A",0,Attendance!R16="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="1"/>
+        <v>0.31</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/24_DS_CLUB_BATCH1_AHM/Attendance.xlsx
+++ b/24_DS_CLUB_BATCH1_AHM/Attendance.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_CLUB_BATCH1_AHM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{959F573E-091A-4FA6-823B-5190A5688702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B66B1462-FC72-4865-8BC3-D13B41CBB2D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
   <sheets>
     <sheet name="Attendance" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="25">
   <si>
     <t>Name</t>
   </si>
@@ -453,14 +453,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -515,8 +515,11 @@
       <c r="R1" s="1">
         <v>45578</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S1" s="1">
+        <v>45613</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -571,8 +574,11 @@
       <c r="R2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -627,10 +633,13 @@
       <c r="R3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
@@ -648,25 +657,25 @@
         <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="I4" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J4" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K4" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L4" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M4" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N4" t="s">
         <v>1</v>
@@ -681,48 +690,51 @@
         <v>1</v>
       </c>
       <c r="R4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="S4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L5" t="s">
         <v>1</v>
       </c>
       <c r="M5" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N5" t="s">
         <v>1</v>
@@ -734,15 +746,18 @@
         <v>1</v>
       </c>
       <c r="Q5" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
@@ -754,7 +769,7 @@
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="s">
         <v>2</v>
@@ -778,89 +793,95 @@
         <v>1</v>
       </c>
       <c r="M6" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N6" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O6" t="s">
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" t="s">
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H7" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7" t="s">
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L7" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M7" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N7" t="s">
         <v>3</v>
       </c>
       <c r="O7" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="S7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="s">
         <v>2</v>
@@ -872,31 +893,31 @@
         <v>3</v>
       </c>
       <c r="G8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P8" t="s">
         <v>2</v>
@@ -905,51 +926,54 @@
         <v>2</v>
       </c>
       <c r="R8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="S8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H9" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I9" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O9" t="s">
         <v>2</v>
@@ -963,10 +987,13 @@
       <c r="R9" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
@@ -975,37 +1002,37 @@
         <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H10" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J10" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M10" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N10" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" t="s">
         <v>2</v>
@@ -1019,78 +1046,84 @@
       <c r="R10" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G11" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H11" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I11" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J11" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K11" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L11" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="M11" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N11" t="s">
         <v>2</v>
       </c>
       <c r="O11" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P11" t="s">
         <v>2</v>
       </c>
       <c r="Q11" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" t="s">
         <v>1</v>
@@ -1099,28 +1132,28 @@
         <v>2</v>
       </c>
       <c r="H12" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J12" t="s">
         <v>2</v>
       </c>
       <c r="K12" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L12" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M12" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N12" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O12" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P12" t="s">
         <v>2</v>
@@ -1129,24 +1162,24 @@
         <v>2</v>
       </c>
       <c r="R12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C13" t="s">
         <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" t="s">
         <v>2</v>
@@ -1187,180 +1220,77 @@
       <c r="R13" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S13" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F14" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G14" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H14" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I14" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J14" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K14" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L14" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M14" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="N14" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O14" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="P14" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Q14" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="R14" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" t="s">
-        <v>2</v>
-      </c>
-      <c r="E15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F15" t="s">
-        <v>2</v>
-      </c>
-      <c r="G15" t="s">
-        <v>2</v>
-      </c>
-      <c r="H15" t="s">
-        <v>2</v>
-      </c>
-      <c r="I15" t="s">
-        <v>2</v>
-      </c>
-      <c r="J15" t="s">
-        <v>2</v>
-      </c>
-      <c r="K15" t="s">
-        <v>2</v>
-      </c>
-      <c r="L15" t="s">
-        <v>2</v>
-      </c>
-      <c r="M15" t="s">
-        <v>2</v>
-      </c>
-      <c r="N15" t="s">
-        <v>2</v>
-      </c>
-      <c r="O15" t="s">
-        <v>2</v>
-      </c>
-      <c r="P15" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>2</v>
-      </c>
-      <c r="R15" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" t="s">
-        <v>12</v>
-      </c>
-      <c r="H16" t="s">
-        <v>12</v>
-      </c>
-      <c r="I16" t="s">
-        <v>12</v>
-      </c>
-      <c r="J16" t="s">
-        <v>12</v>
-      </c>
-      <c r="K16" t="s">
-        <v>12</v>
-      </c>
-      <c r="L16" t="s">
-        <v>12</v>
-      </c>
-      <c r="M16" t="s">
-        <v>12</v>
-      </c>
-      <c r="N16" t="s">
-        <v>12</v>
-      </c>
-      <c r="O16" t="s">
-        <v>12</v>
-      </c>
-      <c r="P16" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>12</v>
-      </c>
-      <c r="R16" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O15">
-    <sortCondition ref="A2:A15"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O13">
+    <sortCondition ref="A2:A13"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1591,77 +1521,77 @@
       <c r="A4" t="s">
         <v>21</v>
       </c>
-      <c r="B4">
-        <f>_xlfn.IFS(Attendance!C4="P",5,Attendance!C4="O",3,Attendance!C4="A",0,Attendance!C4="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <f>_xlfn.IFS(Attendance!D4="P",5,Attendance!D4="O",3,Attendance!D4="A",0,Attendance!D4="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <f>_xlfn.IFS(Attendance!E4="P",5,Attendance!E4="O",3,Attendance!E4="A",0,Attendance!E4="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <f>_xlfn.IFS(Attendance!F4="P",5,Attendance!F4="O",3,Attendance!F4="A",0,Attendance!F4="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <f>_xlfn.IFS(Attendance!G4="P",5,Attendance!G4="O",3,Attendance!G4="A",0,Attendance!G4="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <f>_xlfn.IFS(Attendance!H4="P",5,Attendance!H4="O",3,Attendance!H4="A",0,Attendance!H4="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <f>_xlfn.IFS(Attendance!I4="P",5,Attendance!I4="O",3,Attendance!I4="A",0,Attendance!I4="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <f>_xlfn.IFS(Attendance!J4="P",5,Attendance!J4="O",3,Attendance!J4="A",0,Attendance!J4="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <f>_xlfn.IFS(Attendance!K4="P",5,Attendance!K4="O",3,Attendance!K4="A",0,Attendance!K4="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <f>_xlfn.IFS(Attendance!L4="P",5,Attendance!L4="O",3,Attendance!L4="A",0,Attendance!L4="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <f>_xlfn.IFS(Attendance!M4="P",5,Attendance!M4="O",3,Attendance!M4="A",0,Attendance!M4="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <f>_xlfn.IFS(Attendance!N4="P",5,Attendance!N4="O",3,Attendance!N4="A",0,Attendance!N4="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="N4">
-        <f>_xlfn.IFS(Attendance!O4="P",5,Attendance!O4="O",3,Attendance!O4="A",0,Attendance!O4="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="O4">
-        <f>_xlfn.IFS(Attendance!P4="P",5,Attendance!P4="O",3,Attendance!P4="A",0,Attendance!P4="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="P4">
-        <f>_xlfn.IFS(Attendance!Q4="P",5,Attendance!Q4="O",3,Attendance!Q4="A",0,Attendance!Q4="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="Q4">
-        <f>_xlfn.IFS(Attendance!R4="P",5,Attendance!R4="O",3,Attendance!R4="A",0,Attendance!R4="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="R4">
+      <c r="B4" t="e">
+        <f>_xlfn.IFS(Attendance!#REF!="P",5,Attendance!#REF!="O",3,Attendance!#REF!="A",0,Attendance!#REF!="N/A",0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C4" t="e">
+        <f>_xlfn.IFS(Attendance!#REF!="P",5,Attendance!#REF!="O",3,Attendance!#REF!="A",0,Attendance!#REF!="N/A",0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D4" t="e">
+        <f>_xlfn.IFS(Attendance!#REF!="P",5,Attendance!#REF!="O",3,Attendance!#REF!="A",0,Attendance!#REF!="N/A",0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E4" t="e">
+        <f>_xlfn.IFS(Attendance!#REF!="P",5,Attendance!#REF!="O",3,Attendance!#REF!="A",0,Attendance!#REF!="N/A",0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F4" t="e">
+        <f>_xlfn.IFS(Attendance!#REF!="P",5,Attendance!#REF!="O",3,Attendance!#REF!="A",0,Attendance!#REF!="N/A",0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="G4" t="e">
+        <f>_xlfn.IFS(Attendance!#REF!="P",5,Attendance!#REF!="O",3,Attendance!#REF!="A",0,Attendance!#REF!="N/A",0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H4" t="e">
+        <f>_xlfn.IFS(Attendance!#REF!="P",5,Attendance!#REF!="O",3,Attendance!#REF!="A",0,Attendance!#REF!="N/A",0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I4" t="e">
+        <f>_xlfn.IFS(Attendance!#REF!="P",5,Attendance!#REF!="O",3,Attendance!#REF!="A",0,Attendance!#REF!="N/A",0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J4" t="e">
+        <f>_xlfn.IFS(Attendance!#REF!="P",5,Attendance!#REF!="O",3,Attendance!#REF!="A",0,Attendance!#REF!="N/A",0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K4" t="e">
+        <f>_xlfn.IFS(Attendance!#REF!="P",5,Attendance!#REF!="O",3,Attendance!#REF!="A",0,Attendance!#REF!="N/A",0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L4" t="e">
+        <f>_xlfn.IFS(Attendance!#REF!="P",5,Attendance!#REF!="O",3,Attendance!#REF!="A",0,Attendance!#REF!="N/A",0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="M4" t="e">
+        <f>_xlfn.IFS(Attendance!#REF!="P",5,Attendance!#REF!="O",3,Attendance!#REF!="A",0,Attendance!#REF!="N/A",0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="N4" t="e">
+        <f>_xlfn.IFS(Attendance!#REF!="P",5,Attendance!#REF!="O",3,Attendance!#REF!="A",0,Attendance!#REF!="N/A",0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="O4" t="e">
+        <f>_xlfn.IFS(Attendance!#REF!="P",5,Attendance!#REF!="O",3,Attendance!#REF!="A",0,Attendance!#REF!="N/A",0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="P4" t="e">
+        <f>_xlfn.IFS(Attendance!#REF!="P",5,Attendance!#REF!="O",3,Attendance!#REF!="A",0,Attendance!#REF!="N/A",0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Q4" t="e">
+        <f>_xlfn.IFS(Attendance!#REF!="P",5,Attendance!#REF!="O",3,Attendance!#REF!="A",0,Attendance!#REF!="N/A",0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="R4" t="e">
         <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="S4">
+        <v>#REF!</v>
+      </c>
+      <c r="S4" t="e">
         <f t="shared" si="1"/>
-        <v>1.25</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
@@ -1669,67 +1599,67 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <f>_xlfn.IFS(Attendance!C5="P",5,Attendance!C5="O",3,Attendance!C5="A",0,Attendance!C5="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!C4="P",5,Attendance!C4="O",3,Attendance!C4="A",0,Attendance!C4="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="C5">
-        <f>_xlfn.IFS(Attendance!D5="P",5,Attendance!D5="O",3,Attendance!D5="A",0,Attendance!D5="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!D4="P",5,Attendance!D4="O",3,Attendance!D4="A",0,Attendance!D4="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="D5">
-        <f>_xlfn.IFS(Attendance!E5="P",5,Attendance!E5="O",3,Attendance!E5="A",0,Attendance!E5="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!E4="P",5,Attendance!E4="O",3,Attendance!E4="A",0,Attendance!E4="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="E5">
-        <f>_xlfn.IFS(Attendance!F5="P",5,Attendance!F5="O",3,Attendance!F5="A",0,Attendance!F5="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!F4="P",5,Attendance!F4="O",3,Attendance!F4="A",0,Attendance!F4="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="F5">
-        <f>_xlfn.IFS(Attendance!G5="P",5,Attendance!G5="O",3,Attendance!G5="A",0,Attendance!G5="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!G4="P",5,Attendance!G4="O",3,Attendance!G4="A",0,Attendance!G4="N/A",0)</f>
         <v>3</v>
       </c>
       <c r="G5">
-        <f>_xlfn.IFS(Attendance!H5="P",5,Attendance!H5="O",3,Attendance!H5="A",0,Attendance!H5="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!H4="P",5,Attendance!H4="O",3,Attendance!H4="A",0,Attendance!H4="N/A",0)</f>
         <v>3</v>
       </c>
       <c r="H5">
-        <f>_xlfn.IFS(Attendance!I5="P",5,Attendance!I5="O",3,Attendance!I5="A",0,Attendance!I5="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!I4="P",5,Attendance!I4="O",3,Attendance!I4="A",0,Attendance!I4="N/A",0)</f>
         <v>3</v>
       </c>
       <c r="I5">
-        <f>_xlfn.IFS(Attendance!J5="P",5,Attendance!J5="O",3,Attendance!J5="A",0,Attendance!J5="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!J4="P",5,Attendance!J4="O",3,Attendance!J4="A",0,Attendance!J4="N/A",0)</f>
         <v>3</v>
       </c>
       <c r="J5">
-        <f>_xlfn.IFS(Attendance!K5="P",5,Attendance!K5="O",3,Attendance!K5="A",0,Attendance!K5="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!K4="P",5,Attendance!K4="O",3,Attendance!K4="A",0,Attendance!K4="N/A",0)</f>
         <v>3</v>
       </c>
       <c r="K5">
-        <f>_xlfn.IFS(Attendance!L5="P",5,Attendance!L5="O",3,Attendance!L5="A",0,Attendance!L5="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!L4="P",5,Attendance!L4="O",3,Attendance!L4="A",0,Attendance!L4="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="L5">
-        <f>_xlfn.IFS(Attendance!M5="P",5,Attendance!M5="O",3,Attendance!M5="A",0,Attendance!M5="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!M4="P",5,Attendance!M4="O",3,Attendance!M4="A",0,Attendance!M4="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="M5">
-        <f>_xlfn.IFS(Attendance!N5="P",5,Attendance!N5="O",3,Attendance!N5="A",0,Attendance!N5="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!N4="P",5,Attendance!N4="O",3,Attendance!N4="A",0,Attendance!N4="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="N5">
-        <f>_xlfn.IFS(Attendance!O5="P",5,Attendance!O5="O",3,Attendance!O5="A",0,Attendance!O5="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!O4="P",5,Attendance!O4="O",3,Attendance!O4="A",0,Attendance!O4="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="O5">
-        <f>_xlfn.IFS(Attendance!P5="P",5,Attendance!P5="O",3,Attendance!P5="A",0,Attendance!P5="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!P4="P",5,Attendance!P4="O",3,Attendance!P4="A",0,Attendance!P4="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="P5">
-        <f>_xlfn.IFS(Attendance!Q5="P",5,Attendance!Q5="O",3,Attendance!Q5="A",0,Attendance!Q5="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!Q4="P",5,Attendance!Q4="O",3,Attendance!Q4="A",0,Attendance!Q4="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="Q5">
-        <f>_xlfn.IFS(Attendance!R5="P",5,Attendance!R5="O",3,Attendance!R5="A",0,Attendance!R5="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!R4="P",5,Attendance!R4="O",3,Attendance!R4="A",0,Attendance!R4="N/A",0)</f>
         <v>3</v>
       </c>
       <c r="R5">
@@ -1746,67 +1676,67 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <f>_xlfn.IFS(Attendance!C6="P",5,Attendance!C6="O",3,Attendance!C6="A",0,Attendance!C6="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!C5="P",5,Attendance!C5="O",3,Attendance!C5="A",0,Attendance!C5="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="C6">
-        <f>_xlfn.IFS(Attendance!D6="P",5,Attendance!D6="O",3,Attendance!D6="A",0,Attendance!D6="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!D5="P",5,Attendance!D5="O",3,Attendance!D5="A",0,Attendance!D5="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="D6">
-        <f>_xlfn.IFS(Attendance!E6="P",5,Attendance!E6="O",3,Attendance!E6="A",0,Attendance!E6="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!E5="P",5,Attendance!E5="O",3,Attendance!E5="A",0,Attendance!E5="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="E6">
-        <f>_xlfn.IFS(Attendance!F6="P",5,Attendance!F6="O",3,Attendance!F6="A",0,Attendance!F6="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!F5="P",5,Attendance!F5="O",3,Attendance!F5="A",0,Attendance!F5="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="F6">
-        <f>_xlfn.IFS(Attendance!G6="P",5,Attendance!G6="O",3,Attendance!G6="A",0,Attendance!G6="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!G5="P",5,Attendance!G5="O",3,Attendance!G5="A",0,Attendance!G5="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="G6">
-        <f>_xlfn.IFS(Attendance!H6="P",5,Attendance!H6="O",3,Attendance!H6="A",0,Attendance!H6="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!H5="P",5,Attendance!H5="O",3,Attendance!H5="A",0,Attendance!H5="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="H6">
-        <f>_xlfn.IFS(Attendance!I6="P",5,Attendance!I6="O",3,Attendance!I6="A",0,Attendance!I6="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!I5="P",5,Attendance!I5="O",3,Attendance!I5="A",0,Attendance!I5="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="I6">
-        <f>_xlfn.IFS(Attendance!J6="P",5,Attendance!J6="O",3,Attendance!J6="A",0,Attendance!J6="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!J5="P",5,Attendance!J5="O",3,Attendance!J5="A",0,Attendance!J5="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="J6">
-        <f>_xlfn.IFS(Attendance!K6="P",5,Attendance!K6="O",3,Attendance!K6="A",0,Attendance!K6="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!K5="P",5,Attendance!K5="O",3,Attendance!K5="A",0,Attendance!K5="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="K6">
-        <f>_xlfn.IFS(Attendance!L6="P",5,Attendance!L6="O",3,Attendance!L6="A",0,Attendance!L6="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!L5="P",5,Attendance!L5="O",3,Attendance!L5="A",0,Attendance!L5="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="L6">
-        <f>_xlfn.IFS(Attendance!M6="P",5,Attendance!M6="O",3,Attendance!M6="A",0,Attendance!M6="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!M5="P",5,Attendance!M5="O",3,Attendance!M5="A",0,Attendance!M5="N/A",0)</f>
         <v>3</v>
       </c>
       <c r="M6">
-        <f>_xlfn.IFS(Attendance!N6="P",5,Attendance!N6="O",3,Attendance!N6="A",0,Attendance!N6="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!N5="P",5,Attendance!N5="O",3,Attendance!N5="A",0,Attendance!N5="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="N6">
-        <f>_xlfn.IFS(Attendance!O6="P",5,Attendance!O6="O",3,Attendance!O6="A",0,Attendance!O6="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!O5="P",5,Attendance!O5="O",3,Attendance!O5="A",0,Attendance!O5="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="O6">
-        <f>_xlfn.IFS(Attendance!P6="P",5,Attendance!P6="O",3,Attendance!P6="A",0,Attendance!P6="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!P5="P",5,Attendance!P5="O",3,Attendance!P5="A",0,Attendance!P5="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="P6">
-        <f>_xlfn.IFS(Attendance!Q6="P",5,Attendance!Q6="O",3,Attendance!Q6="A",0,Attendance!Q6="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!Q5="P",5,Attendance!Q5="O",3,Attendance!Q5="A",0,Attendance!Q5="N/A",0)</f>
         <v>3</v>
       </c>
       <c r="Q6">
-        <f>_xlfn.IFS(Attendance!R6="P",5,Attendance!R6="O",3,Attendance!R6="A",0,Attendance!R6="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!R5="P",5,Attendance!R5="O",3,Attendance!R5="A",0,Attendance!R5="N/A",0)</f>
         <v>3</v>
       </c>
       <c r="R6">
@@ -1823,67 +1753,67 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <f>_xlfn.IFS(Attendance!C7="P",5,Attendance!C7="O",3,Attendance!C7="A",0,Attendance!C7="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!C6="P",5,Attendance!C6="O",3,Attendance!C6="A",0,Attendance!C6="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="C7">
-        <f>_xlfn.IFS(Attendance!D7="P",5,Attendance!D7="O",3,Attendance!D7="A",0,Attendance!D7="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!D6="P",5,Attendance!D6="O",3,Attendance!D6="A",0,Attendance!D6="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="D7">
-        <f>_xlfn.IFS(Attendance!E7="P",5,Attendance!E7="O",3,Attendance!E7="A",0,Attendance!E7="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!E6="P",5,Attendance!E6="O",3,Attendance!E6="A",0,Attendance!E6="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="E7">
-        <f>_xlfn.IFS(Attendance!F7="P",5,Attendance!F7="O",3,Attendance!F7="A",0,Attendance!F7="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!F6="P",5,Attendance!F6="O",3,Attendance!F6="A",0,Attendance!F6="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="F7">
-        <f>_xlfn.IFS(Attendance!G7="P",5,Attendance!G7="O",3,Attendance!G7="A",0,Attendance!G7="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!G6="P",5,Attendance!G6="O",3,Attendance!G6="A",0,Attendance!G6="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="G7">
-        <f>_xlfn.IFS(Attendance!H7="P",5,Attendance!H7="O",3,Attendance!H7="A",0,Attendance!H7="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!H6="P",5,Attendance!H6="O",3,Attendance!H6="A",0,Attendance!H6="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="H7">
-        <f>_xlfn.IFS(Attendance!I7="P",5,Attendance!I7="O",3,Attendance!I7="A",0,Attendance!I7="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!I6="P",5,Attendance!I6="O",3,Attendance!I6="A",0,Attendance!I6="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="I7">
-        <f>_xlfn.IFS(Attendance!J7="P",5,Attendance!J7="O",3,Attendance!J7="A",0,Attendance!J7="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!J6="P",5,Attendance!J6="O",3,Attendance!J6="A",0,Attendance!J6="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="J7">
-        <f>_xlfn.IFS(Attendance!K7="P",5,Attendance!K7="O",3,Attendance!K7="A",0,Attendance!K7="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!K6="P",5,Attendance!K6="O",3,Attendance!K6="A",0,Attendance!K6="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="K7">
-        <f>_xlfn.IFS(Attendance!L7="P",5,Attendance!L7="O",3,Attendance!L7="A",0,Attendance!L7="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!L6="P",5,Attendance!L6="O",3,Attendance!L6="A",0,Attendance!L6="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="L7">
-        <f>_xlfn.IFS(Attendance!M7="P",5,Attendance!M7="O",3,Attendance!M7="A",0,Attendance!M7="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!M6="P",5,Attendance!M6="O",3,Attendance!M6="A",0,Attendance!M6="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="M7">
-        <f>_xlfn.IFS(Attendance!N7="P",5,Attendance!N7="O",3,Attendance!N7="A",0,Attendance!N7="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!N6="P",5,Attendance!N6="O",3,Attendance!N6="A",0,Attendance!N6="N/A",0)</f>
         <v>3</v>
       </c>
       <c r="N7">
-        <f>_xlfn.IFS(Attendance!O7="P",5,Attendance!O7="O",3,Attendance!O7="A",0,Attendance!O7="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!O6="P",5,Attendance!O6="O",3,Attendance!O6="A",0,Attendance!O6="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="O7">
-        <f>_xlfn.IFS(Attendance!P7="P",5,Attendance!P7="O",3,Attendance!P7="A",0,Attendance!P7="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!P6="P",5,Attendance!P6="O",3,Attendance!P6="A",0,Attendance!P6="N/A",0)</f>
         <v>3</v>
       </c>
       <c r="P7">
-        <f>_xlfn.IFS(Attendance!Q7="P",5,Attendance!Q7="O",3,Attendance!Q7="A",0,Attendance!Q7="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!Q6="P",5,Attendance!Q6="O",3,Attendance!Q6="A",0,Attendance!Q6="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="Q7">
-        <f>_xlfn.IFS(Attendance!R7="P",5,Attendance!R7="O",3,Attendance!R7="A",0,Attendance!R7="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!R6="P",5,Attendance!R6="O",3,Attendance!R6="A",0,Attendance!R6="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="R7">
@@ -1900,67 +1830,67 @@
         <v>4</v>
       </c>
       <c r="B8">
-        <f>_xlfn.IFS(Attendance!C8="P",5,Attendance!C8="O",3,Attendance!C8="A",0,Attendance!C8="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!C7="P",5,Attendance!C7="O",3,Attendance!C7="A",0,Attendance!C7="N/A",0)</f>
         <v>3</v>
       </c>
       <c r="C8">
-        <f>_xlfn.IFS(Attendance!D8="P",5,Attendance!D8="O",3,Attendance!D8="A",0,Attendance!D8="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!D7="P",5,Attendance!D7="O",3,Attendance!D7="A",0,Attendance!D7="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="D8">
-        <f>_xlfn.IFS(Attendance!E8="P",5,Attendance!E8="O",3,Attendance!E8="A",0,Attendance!E8="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!E7="P",5,Attendance!E7="O",3,Attendance!E7="A",0,Attendance!E7="N/A",0)</f>
         <v>3</v>
       </c>
       <c r="E8">
-        <f>_xlfn.IFS(Attendance!F8="P",5,Attendance!F8="O",3,Attendance!F8="A",0,Attendance!F8="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!F7="P",5,Attendance!F7="O",3,Attendance!F7="A",0,Attendance!F7="N/A",0)</f>
         <v>3</v>
       </c>
       <c r="F8">
-        <f>_xlfn.IFS(Attendance!G8="P",5,Attendance!G8="O",3,Attendance!G8="A",0,Attendance!G8="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!G7="P",5,Attendance!G7="O",3,Attendance!G7="A",0,Attendance!G7="N/A",0)</f>
         <v>3</v>
       </c>
       <c r="G8">
-        <f>_xlfn.IFS(Attendance!H8="P",5,Attendance!H8="O",3,Attendance!H8="A",0,Attendance!H8="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!H7="P",5,Attendance!H7="O",3,Attendance!H7="A",0,Attendance!H7="N/A",0)</f>
         <v>3</v>
       </c>
       <c r="H8">
-        <f>_xlfn.IFS(Attendance!I8="P",5,Attendance!I8="O",3,Attendance!I8="A",0,Attendance!I8="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!I7="P",5,Attendance!I7="O",3,Attendance!I7="A",0,Attendance!I7="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="I8">
-        <f>_xlfn.IFS(Attendance!J8="P",5,Attendance!J8="O",3,Attendance!J8="A",0,Attendance!J8="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!J7="P",5,Attendance!J7="O",3,Attendance!J7="A",0,Attendance!J7="N/A",0)</f>
         <v>3</v>
       </c>
       <c r="J8">
-        <f>_xlfn.IFS(Attendance!K8="P",5,Attendance!K8="O",3,Attendance!K8="A",0,Attendance!K8="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!K7="P",5,Attendance!K7="O",3,Attendance!K7="A",0,Attendance!K7="N/A",0)</f>
         <v>3</v>
       </c>
       <c r="K8">
-        <f>_xlfn.IFS(Attendance!L8="P",5,Attendance!L8="O",3,Attendance!L8="A",0,Attendance!L8="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!L7="P",5,Attendance!L7="O",3,Attendance!L7="A",0,Attendance!L7="N/A",0)</f>
         <v>3</v>
       </c>
       <c r="L8">
-        <f>_xlfn.IFS(Attendance!M8="P",5,Attendance!M8="O",3,Attendance!M8="A",0,Attendance!M8="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!M7="P",5,Attendance!M7="O",3,Attendance!M7="A",0,Attendance!M7="N/A",0)</f>
         <v>3</v>
       </c>
       <c r="M8">
-        <f>_xlfn.IFS(Attendance!N8="P",5,Attendance!N8="O",3,Attendance!N8="A",0,Attendance!N8="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!N7="P",5,Attendance!N7="O",3,Attendance!N7="A",0,Attendance!N7="N/A",0)</f>
         <v>3</v>
       </c>
       <c r="N8">
-        <f>_xlfn.IFS(Attendance!O8="P",5,Attendance!O8="O",3,Attendance!O8="A",0,Attendance!O8="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!O7="P",5,Attendance!O7="O",3,Attendance!O7="A",0,Attendance!O7="N/A",0)</f>
         <v>3</v>
       </c>
       <c r="O8">
-        <f>_xlfn.IFS(Attendance!P8="P",5,Attendance!P8="O",3,Attendance!P8="A",0,Attendance!P8="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!P7="P",5,Attendance!P7="O",3,Attendance!P7="A",0,Attendance!P7="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="P8">
-        <f>_xlfn.IFS(Attendance!Q8="P",5,Attendance!Q8="O",3,Attendance!Q8="A",0,Attendance!Q8="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!Q7="P",5,Attendance!Q7="O",3,Attendance!Q7="A",0,Attendance!Q7="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="Q8">
-        <f>_xlfn.IFS(Attendance!R8="P",5,Attendance!R8="O",3,Attendance!R8="A",0,Attendance!R8="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!R7="P",5,Attendance!R7="O",3,Attendance!R7="A",0,Attendance!R7="N/A",0)</f>
         <v>3</v>
       </c>
       <c r="R8">
@@ -1977,67 +1907,67 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <f>_xlfn.IFS(Attendance!C9="P",5,Attendance!C9="O",3,Attendance!C9="A",0,Attendance!C9="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!C8="P",5,Attendance!C8="O",3,Attendance!C8="A",0,Attendance!C8="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="C9">
-        <f>_xlfn.IFS(Attendance!D9="P",5,Attendance!D9="O",3,Attendance!D9="A",0,Attendance!D9="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!D8="P",5,Attendance!D8="O",3,Attendance!D8="A",0,Attendance!D8="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="D9">
-        <f>_xlfn.IFS(Attendance!E9="P",5,Attendance!E9="O",3,Attendance!E9="A",0,Attendance!E9="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!E8="P",5,Attendance!E8="O",3,Attendance!E8="A",0,Attendance!E8="N/A",0)</f>
         <v>3</v>
       </c>
       <c r="E9">
-        <f>_xlfn.IFS(Attendance!F9="P",5,Attendance!F9="O",3,Attendance!F9="A",0,Attendance!F9="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!F8="P",5,Attendance!F8="O",3,Attendance!F8="A",0,Attendance!F8="N/A",0)</f>
         <v>3</v>
       </c>
       <c r="F9">
-        <f>_xlfn.IFS(Attendance!G9="P",5,Attendance!G9="O",3,Attendance!G9="A",0,Attendance!G9="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!G8="P",5,Attendance!G8="O",3,Attendance!G8="A",0,Attendance!G8="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="G9">
-        <f>_xlfn.IFS(Attendance!H9="P",5,Attendance!H9="O",3,Attendance!H9="A",0,Attendance!H9="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!H8="P",5,Attendance!H8="O",3,Attendance!H8="A",0,Attendance!H8="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="H9">
-        <f>_xlfn.IFS(Attendance!I9="P",5,Attendance!I9="O",3,Attendance!I9="A",0,Attendance!I9="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!I8="P",5,Attendance!I8="O",3,Attendance!I8="A",0,Attendance!I8="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="I9">
-        <f>_xlfn.IFS(Attendance!J9="P",5,Attendance!J9="O",3,Attendance!J9="A",0,Attendance!J9="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!J8="P",5,Attendance!J8="O",3,Attendance!J8="A",0,Attendance!J8="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="J9">
-        <f>_xlfn.IFS(Attendance!K9="P",5,Attendance!K9="O",3,Attendance!K9="A",0,Attendance!K9="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!K8="P",5,Attendance!K8="O",3,Attendance!K8="A",0,Attendance!K8="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="K9">
-        <f>_xlfn.IFS(Attendance!L9="P",5,Attendance!L9="O",3,Attendance!L9="A",0,Attendance!L9="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!L8="P",5,Attendance!L8="O",3,Attendance!L8="A",0,Attendance!L8="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="L9">
-        <f>_xlfn.IFS(Attendance!M9="P",5,Attendance!M9="O",3,Attendance!M9="A",0,Attendance!M9="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!M8="P",5,Attendance!M8="O",3,Attendance!M8="A",0,Attendance!M8="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="M9">
-        <f>_xlfn.IFS(Attendance!N9="P",5,Attendance!N9="O",3,Attendance!N9="A",0,Attendance!N9="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!N8="P",5,Attendance!N8="O",3,Attendance!N8="A",0,Attendance!N8="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="N9">
-        <f>_xlfn.IFS(Attendance!O9="P",5,Attendance!O9="O",3,Attendance!O9="A",0,Attendance!O9="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!O8="P",5,Attendance!O8="O",3,Attendance!O8="A",0,Attendance!O8="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="O9">
-        <f>_xlfn.IFS(Attendance!P9="P",5,Attendance!P9="O",3,Attendance!P9="A",0,Attendance!P9="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!P8="P",5,Attendance!P8="O",3,Attendance!P8="A",0,Attendance!P8="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="P9">
-        <f>_xlfn.IFS(Attendance!Q9="P",5,Attendance!Q9="O",3,Attendance!Q9="A",0,Attendance!Q9="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!Q8="P",5,Attendance!Q8="O",3,Attendance!Q8="A",0,Attendance!Q8="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="Q9">
-        <f>_xlfn.IFS(Attendance!R9="P",5,Attendance!R9="O",3,Attendance!R9="A",0,Attendance!R9="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!R8="P",5,Attendance!R8="O",3,Attendance!R8="A",0,Attendance!R8="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="R9">
@@ -2054,67 +1984,67 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <f>_xlfn.IFS(Attendance!C10="P",5,Attendance!C10="O",3,Attendance!C10="A",0,Attendance!C10="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!C9="P",5,Attendance!C9="O",3,Attendance!C9="A",0,Attendance!C9="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="C10">
-        <f>_xlfn.IFS(Attendance!D10="P",5,Attendance!D10="O",3,Attendance!D10="A",0,Attendance!D10="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!D9="P",5,Attendance!D9="O",3,Attendance!D9="A",0,Attendance!D9="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="D10">
-        <f>_xlfn.IFS(Attendance!E10="P",5,Attendance!E10="O",3,Attendance!E10="A",0,Attendance!E10="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!E9="P",5,Attendance!E9="O",3,Attendance!E9="A",0,Attendance!E9="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="E10">
-        <f>_xlfn.IFS(Attendance!F10="P",5,Attendance!F10="O",3,Attendance!F10="A",0,Attendance!F10="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!F9="P",5,Attendance!F9="O",3,Attendance!F9="A",0,Attendance!F9="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="F10">
-        <f>_xlfn.IFS(Attendance!G10="P",5,Attendance!G10="O",3,Attendance!G10="A",0,Attendance!G10="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!G9="P",5,Attendance!G9="O",3,Attendance!G9="A",0,Attendance!G9="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="G10">
-        <f>_xlfn.IFS(Attendance!H10="P",5,Attendance!H10="O",3,Attendance!H10="A",0,Attendance!H10="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!H9="P",5,Attendance!H9="O",3,Attendance!H9="A",0,Attendance!H9="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="H10">
-        <f>_xlfn.IFS(Attendance!I10="P",5,Attendance!I10="O",3,Attendance!I10="A",0,Attendance!I10="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!I9="P",5,Attendance!I9="O",3,Attendance!I9="A",0,Attendance!I9="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="I10">
-        <f>_xlfn.IFS(Attendance!J10="P",5,Attendance!J10="O",3,Attendance!J10="A",0,Attendance!J10="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!J9="P",5,Attendance!J9="O",3,Attendance!J9="A",0,Attendance!J9="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="J10">
-        <f>_xlfn.IFS(Attendance!K10="P",5,Attendance!K10="O",3,Attendance!K10="A",0,Attendance!K10="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!K9="P",5,Attendance!K9="O",3,Attendance!K9="A",0,Attendance!K9="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="K10">
-        <f>_xlfn.IFS(Attendance!L10="P",5,Attendance!L10="O",3,Attendance!L10="A",0,Attendance!L10="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!L9="P",5,Attendance!L9="O",3,Attendance!L9="A",0,Attendance!L9="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="L10">
-        <f>_xlfn.IFS(Attendance!M10="P",5,Attendance!M10="O",3,Attendance!M10="A",0,Attendance!M10="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!M9="P",5,Attendance!M9="O",3,Attendance!M9="A",0,Attendance!M9="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="M10">
-        <f>_xlfn.IFS(Attendance!N10="P",5,Attendance!N10="O",3,Attendance!N10="A",0,Attendance!N10="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!N9="P",5,Attendance!N9="O",3,Attendance!N9="A",0,Attendance!N9="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="N10">
-        <f>_xlfn.IFS(Attendance!O10="P",5,Attendance!O10="O",3,Attendance!O10="A",0,Attendance!O10="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!O9="P",5,Attendance!O9="O",3,Attendance!O9="A",0,Attendance!O9="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="O10">
-        <f>_xlfn.IFS(Attendance!P10="P",5,Attendance!P10="O",3,Attendance!P10="A",0,Attendance!P10="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!P9="P",5,Attendance!P9="O",3,Attendance!P9="A",0,Attendance!P9="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="P10">
-        <f>_xlfn.IFS(Attendance!Q10="P",5,Attendance!Q10="O",3,Attendance!Q10="A",0,Attendance!Q10="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!Q9="P",5,Attendance!Q9="O",3,Attendance!Q9="A",0,Attendance!Q9="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="Q10">
-        <f>_xlfn.IFS(Attendance!R10="P",5,Attendance!R10="O",3,Attendance!R10="A",0,Attendance!R10="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!R9="P",5,Attendance!R9="O",3,Attendance!R9="A",0,Attendance!R9="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="R10">
@@ -2130,77 +2060,77 @@
       <c r="A11" t="s">
         <v>18</v>
       </c>
-      <c r="B11">
-        <f>_xlfn.IFS(Attendance!C11="P",5,Attendance!C11="O",3,Attendance!C11="A",0,Attendance!C11="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <f>_xlfn.IFS(Attendance!D11="P",5,Attendance!D11="O",3,Attendance!D11="A",0,Attendance!D11="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <f>_xlfn.IFS(Attendance!E11="P",5,Attendance!E11="O",3,Attendance!E11="A",0,Attendance!E11="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <f>_xlfn.IFS(Attendance!F11="P",5,Attendance!F11="O",3,Attendance!F11="A",0,Attendance!F11="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <f>_xlfn.IFS(Attendance!G11="P",5,Attendance!G11="O",3,Attendance!G11="A",0,Attendance!G11="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <f>_xlfn.IFS(Attendance!H11="P",5,Attendance!H11="O",3,Attendance!H11="A",0,Attendance!H11="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <f>_xlfn.IFS(Attendance!I11="P",5,Attendance!I11="O",3,Attendance!I11="A",0,Attendance!I11="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <f>_xlfn.IFS(Attendance!J11="P",5,Attendance!J11="O",3,Attendance!J11="A",0,Attendance!J11="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <f>_xlfn.IFS(Attendance!K11="P",5,Attendance!K11="O",3,Attendance!K11="A",0,Attendance!K11="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <f>_xlfn.IFS(Attendance!L11="P",5,Attendance!L11="O",3,Attendance!L11="A",0,Attendance!L11="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <f>_xlfn.IFS(Attendance!M11="P",5,Attendance!M11="O",3,Attendance!M11="A",0,Attendance!M11="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="M11">
-        <f>_xlfn.IFS(Attendance!N11="P",5,Attendance!N11="O",3,Attendance!N11="A",0,Attendance!N11="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <f>_xlfn.IFS(Attendance!O11="P",5,Attendance!O11="O",3,Attendance!O11="A",0,Attendance!O11="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="O11">
-        <f>_xlfn.IFS(Attendance!P11="P",5,Attendance!P11="O",3,Attendance!P11="A",0,Attendance!P11="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <f>_xlfn.IFS(Attendance!Q11="P",5,Attendance!Q11="O",3,Attendance!Q11="A",0,Attendance!Q11="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="Q11">
-        <f>_xlfn.IFS(Attendance!R11="P",5,Attendance!R11="O",3,Attendance!R11="A",0,Attendance!R11="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="R11">
+      <c r="B11" t="e">
+        <f>_xlfn.IFS(Attendance!#REF!="P",5,Attendance!#REF!="O",3,Attendance!#REF!="A",0,Attendance!#REF!="N/A",0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C11" t="e">
+        <f>_xlfn.IFS(Attendance!#REF!="P",5,Attendance!#REF!="O",3,Attendance!#REF!="A",0,Attendance!#REF!="N/A",0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D11" t="e">
+        <f>_xlfn.IFS(Attendance!#REF!="P",5,Attendance!#REF!="O",3,Attendance!#REF!="A",0,Attendance!#REF!="N/A",0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E11" t="e">
+        <f>_xlfn.IFS(Attendance!#REF!="P",5,Attendance!#REF!="O",3,Attendance!#REF!="A",0,Attendance!#REF!="N/A",0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F11" t="e">
+        <f>_xlfn.IFS(Attendance!#REF!="P",5,Attendance!#REF!="O",3,Attendance!#REF!="A",0,Attendance!#REF!="N/A",0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="G11" t="e">
+        <f>_xlfn.IFS(Attendance!#REF!="P",5,Attendance!#REF!="O",3,Attendance!#REF!="A",0,Attendance!#REF!="N/A",0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H11" t="e">
+        <f>_xlfn.IFS(Attendance!#REF!="P",5,Attendance!#REF!="O",3,Attendance!#REF!="A",0,Attendance!#REF!="N/A",0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I11" t="e">
+        <f>_xlfn.IFS(Attendance!#REF!="P",5,Attendance!#REF!="O",3,Attendance!#REF!="A",0,Attendance!#REF!="N/A",0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J11" t="e">
+        <f>_xlfn.IFS(Attendance!#REF!="P",5,Attendance!#REF!="O",3,Attendance!#REF!="A",0,Attendance!#REF!="N/A",0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K11" t="e">
+        <f>_xlfn.IFS(Attendance!#REF!="P",5,Attendance!#REF!="O",3,Attendance!#REF!="A",0,Attendance!#REF!="N/A",0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L11" t="e">
+        <f>_xlfn.IFS(Attendance!#REF!="P",5,Attendance!#REF!="O",3,Attendance!#REF!="A",0,Attendance!#REF!="N/A",0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="M11" t="e">
+        <f>_xlfn.IFS(Attendance!#REF!="P",5,Attendance!#REF!="O",3,Attendance!#REF!="A",0,Attendance!#REF!="N/A",0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="N11" t="e">
+        <f>_xlfn.IFS(Attendance!#REF!="P",5,Attendance!#REF!="O",3,Attendance!#REF!="A",0,Attendance!#REF!="N/A",0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="O11" t="e">
+        <f>_xlfn.IFS(Attendance!#REF!="P",5,Attendance!#REF!="O",3,Attendance!#REF!="A",0,Attendance!#REF!="N/A",0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="P11" t="e">
+        <f>_xlfn.IFS(Attendance!#REF!="P",5,Attendance!#REF!="O",3,Attendance!#REF!="A",0,Attendance!#REF!="N/A",0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Q11" t="e">
+        <f>_xlfn.IFS(Attendance!#REF!="P",5,Attendance!#REF!="O",3,Attendance!#REF!="A",0,Attendance!#REF!="N/A",0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="R11" t="e">
         <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="S11">
+        <v>#REF!</v>
+      </c>
+      <c r="S11" t="e">
         <f t="shared" si="1"/>
-        <v>0.94</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
@@ -2208,67 +2138,67 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <f>_xlfn.IFS(Attendance!C12="P",5,Attendance!C12="O",3,Attendance!C12="A",0,Attendance!C12="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!C10="P",5,Attendance!C10="O",3,Attendance!C10="A",0,Attendance!C10="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="C12">
-        <f>_xlfn.IFS(Attendance!D12="P",5,Attendance!D12="O",3,Attendance!D12="A",0,Attendance!D12="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!D10="P",5,Attendance!D10="O",3,Attendance!D10="A",0,Attendance!D10="N/A",0)</f>
         <v>3</v>
       </c>
       <c r="D12">
-        <f>_xlfn.IFS(Attendance!E12="P",5,Attendance!E12="O",3,Attendance!E12="A",0,Attendance!E12="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!E10="P",5,Attendance!E10="O",3,Attendance!E10="A",0,Attendance!E10="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="E12">
-        <f>_xlfn.IFS(Attendance!F12="P",5,Attendance!F12="O",3,Attendance!F12="A",0,Attendance!F12="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!F10="P",5,Attendance!F10="O",3,Attendance!F10="A",0,Attendance!F10="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="F12">
-        <f>_xlfn.IFS(Attendance!G12="P",5,Attendance!G12="O",3,Attendance!G12="A",0,Attendance!G12="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!G10="P",5,Attendance!G10="O",3,Attendance!G10="A",0,Attendance!G10="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="G12">
-        <f>_xlfn.IFS(Attendance!H12="P",5,Attendance!H12="O",3,Attendance!H12="A",0,Attendance!H12="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!H10="P",5,Attendance!H10="O",3,Attendance!H10="A",0,Attendance!H10="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="H12">
-        <f>_xlfn.IFS(Attendance!I12="P",5,Attendance!I12="O",3,Attendance!I12="A",0,Attendance!I12="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!I10="P",5,Attendance!I10="O",3,Attendance!I10="A",0,Attendance!I10="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="I12">
-        <f>_xlfn.IFS(Attendance!J12="P",5,Attendance!J12="O",3,Attendance!J12="A",0,Attendance!J12="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!J10="P",5,Attendance!J10="O",3,Attendance!J10="A",0,Attendance!J10="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="J12">
-        <f>_xlfn.IFS(Attendance!K12="P",5,Attendance!K12="O",3,Attendance!K12="A",0,Attendance!K12="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!K10="P",5,Attendance!K10="O",3,Attendance!K10="A",0,Attendance!K10="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="K12">
-        <f>_xlfn.IFS(Attendance!L12="P",5,Attendance!L12="O",3,Attendance!L12="A",0,Attendance!L12="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!L10="P",5,Attendance!L10="O",3,Attendance!L10="A",0,Attendance!L10="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="L12">
-        <f>_xlfn.IFS(Attendance!M12="P",5,Attendance!M12="O",3,Attendance!M12="A",0,Attendance!M12="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!M10="P",5,Attendance!M10="O",3,Attendance!M10="A",0,Attendance!M10="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="M12">
-        <f>_xlfn.IFS(Attendance!N12="P",5,Attendance!N12="O",3,Attendance!N12="A",0,Attendance!N12="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!N10="P",5,Attendance!N10="O",3,Attendance!N10="A",0,Attendance!N10="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="N12">
-        <f>_xlfn.IFS(Attendance!O12="P",5,Attendance!O12="O",3,Attendance!O12="A",0,Attendance!O12="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!O10="P",5,Attendance!O10="O",3,Attendance!O10="A",0,Attendance!O10="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="O12">
-        <f>_xlfn.IFS(Attendance!P12="P",5,Attendance!P12="O",3,Attendance!P12="A",0,Attendance!P12="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!P10="P",5,Attendance!P10="O",3,Attendance!P10="A",0,Attendance!P10="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="P12">
-        <f>_xlfn.IFS(Attendance!Q12="P",5,Attendance!Q12="O",3,Attendance!Q12="A",0,Attendance!Q12="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!Q10="P",5,Attendance!Q10="O",3,Attendance!Q10="A",0,Attendance!Q10="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="Q12">
-        <f>_xlfn.IFS(Attendance!R12="P",5,Attendance!R12="O",3,Attendance!R12="A",0,Attendance!R12="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!R10="P",5,Attendance!R10="O",3,Attendance!R10="A",0,Attendance!R10="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="R12">
@@ -2285,67 +2215,67 @@
         <v>10</v>
       </c>
       <c r="B13">
-        <f>_xlfn.IFS(Attendance!C13="P",5,Attendance!C13="O",3,Attendance!C13="A",0,Attendance!C13="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!C11="P",5,Attendance!C11="O",3,Attendance!C11="A",0,Attendance!C11="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="C13">
-        <f>_xlfn.IFS(Attendance!D13="P",5,Attendance!D13="O",3,Attendance!D13="A",0,Attendance!D13="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!D11="P",5,Attendance!D11="O",3,Attendance!D11="A",0,Attendance!D11="N/A",0)</f>
         <v>3</v>
       </c>
       <c r="D13">
-        <f>_xlfn.IFS(Attendance!E13="P",5,Attendance!E13="O",3,Attendance!E13="A",0,Attendance!E13="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!E11="P",5,Attendance!E11="O",3,Attendance!E11="A",0,Attendance!E11="N/A",0)</f>
         <v>3</v>
       </c>
       <c r="E13">
-        <f>_xlfn.IFS(Attendance!F13="P",5,Attendance!F13="O",3,Attendance!F13="A",0,Attendance!F13="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!F11="P",5,Attendance!F11="O",3,Attendance!F11="A",0,Attendance!F11="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="F13">
-        <f>_xlfn.IFS(Attendance!G13="P",5,Attendance!G13="O",3,Attendance!G13="A",0,Attendance!G13="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!G11="P",5,Attendance!G11="O",3,Attendance!G11="A",0,Attendance!G11="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="G13">
-        <f>_xlfn.IFS(Attendance!H13="P",5,Attendance!H13="O",3,Attendance!H13="A",0,Attendance!H13="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!H11="P",5,Attendance!H11="O",3,Attendance!H11="A",0,Attendance!H11="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="H13">
-        <f>_xlfn.IFS(Attendance!I13="P",5,Attendance!I13="O",3,Attendance!I13="A",0,Attendance!I13="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!I11="P",5,Attendance!I11="O",3,Attendance!I11="A",0,Attendance!I11="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="I13">
-        <f>_xlfn.IFS(Attendance!J13="P",5,Attendance!J13="O",3,Attendance!J13="A",0,Attendance!J13="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!J11="P",5,Attendance!J11="O",3,Attendance!J11="A",0,Attendance!J11="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="J13">
-        <f>_xlfn.IFS(Attendance!K13="P",5,Attendance!K13="O",3,Attendance!K13="A",0,Attendance!K13="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!K11="P",5,Attendance!K11="O",3,Attendance!K11="A",0,Attendance!K11="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="K13">
-        <f>_xlfn.IFS(Attendance!L13="P",5,Attendance!L13="O",3,Attendance!L13="A",0,Attendance!L13="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!L11="P",5,Attendance!L11="O",3,Attendance!L11="A",0,Attendance!L11="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="L13">
-        <f>_xlfn.IFS(Attendance!M13="P",5,Attendance!M13="O",3,Attendance!M13="A",0,Attendance!M13="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!M11="P",5,Attendance!M11="O",3,Attendance!M11="A",0,Attendance!M11="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="M13">
-        <f>_xlfn.IFS(Attendance!N13="P",5,Attendance!N13="O",3,Attendance!N13="A",0,Attendance!N13="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!N11="P",5,Attendance!N11="O",3,Attendance!N11="A",0,Attendance!N11="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="N13">
-        <f>_xlfn.IFS(Attendance!O13="P",5,Attendance!O13="O",3,Attendance!O13="A",0,Attendance!O13="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!O11="P",5,Attendance!O11="O",3,Attendance!O11="A",0,Attendance!O11="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="O13">
-        <f>_xlfn.IFS(Attendance!P13="P",5,Attendance!P13="O",3,Attendance!P13="A",0,Attendance!P13="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!P11="P",5,Attendance!P11="O",3,Attendance!P11="A",0,Attendance!P11="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="P13">
-        <f>_xlfn.IFS(Attendance!Q13="P",5,Attendance!Q13="O",3,Attendance!Q13="A",0,Attendance!Q13="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!Q11="P",5,Attendance!Q11="O",3,Attendance!Q11="A",0,Attendance!Q11="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="Q13">
-        <f>_xlfn.IFS(Attendance!R13="P",5,Attendance!R13="O",3,Attendance!R13="A",0,Attendance!R13="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!R11="P",5,Attendance!R11="O",3,Attendance!R11="A",0,Attendance!R11="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="R13">
@@ -2362,67 +2292,67 @@
         <v>6</v>
       </c>
       <c r="B14">
-        <f>_xlfn.IFS(Attendance!C14="P",5,Attendance!C14="O",3,Attendance!C14="A",0,Attendance!C14="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!C12="P",5,Attendance!C12="O",3,Attendance!C12="A",0,Attendance!C12="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="C14">
-        <f>_xlfn.IFS(Attendance!D14="P",5,Attendance!D14="O",3,Attendance!D14="A",0,Attendance!D14="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!D12="P",5,Attendance!D12="O",3,Attendance!D12="A",0,Attendance!D12="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="D14">
-        <f>_xlfn.IFS(Attendance!E14="P",5,Attendance!E14="O",3,Attendance!E14="A",0,Attendance!E14="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!E12="P",5,Attendance!E12="O",3,Attendance!E12="A",0,Attendance!E12="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="E14">
-        <f>_xlfn.IFS(Attendance!F14="P",5,Attendance!F14="O",3,Attendance!F14="A",0,Attendance!F14="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!F12="P",5,Attendance!F12="O",3,Attendance!F12="A",0,Attendance!F12="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="F14">
-        <f>_xlfn.IFS(Attendance!G14="P",5,Attendance!G14="O",3,Attendance!G14="A",0,Attendance!G14="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!G12="P",5,Attendance!G12="O",3,Attendance!G12="A",0,Attendance!G12="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="G14">
-        <f>_xlfn.IFS(Attendance!H14="P",5,Attendance!H14="O",3,Attendance!H14="A",0,Attendance!H14="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!H12="P",5,Attendance!H12="O",3,Attendance!H12="A",0,Attendance!H12="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="H14">
-        <f>_xlfn.IFS(Attendance!I14="P",5,Attendance!I14="O",3,Attendance!I14="A",0,Attendance!I14="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!I12="P",5,Attendance!I12="O",3,Attendance!I12="A",0,Attendance!I12="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="I14">
-        <f>_xlfn.IFS(Attendance!J14="P",5,Attendance!J14="O",3,Attendance!J14="A",0,Attendance!J14="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!J12="P",5,Attendance!J12="O",3,Attendance!J12="A",0,Attendance!J12="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="J14">
-        <f>_xlfn.IFS(Attendance!K14="P",5,Attendance!K14="O",3,Attendance!K14="A",0,Attendance!K14="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!K12="P",5,Attendance!K12="O",3,Attendance!K12="A",0,Attendance!K12="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="K14">
-        <f>_xlfn.IFS(Attendance!L14="P",5,Attendance!L14="O",3,Attendance!L14="A",0,Attendance!L14="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!L12="P",5,Attendance!L12="O",3,Attendance!L12="A",0,Attendance!L12="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="L14">
-        <f>_xlfn.IFS(Attendance!M14="P",5,Attendance!M14="O",3,Attendance!M14="A",0,Attendance!M14="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!M12="P",5,Attendance!M12="O",3,Attendance!M12="A",0,Attendance!M12="N/A",0)</f>
         <v>3</v>
       </c>
       <c r="M14">
-        <f>_xlfn.IFS(Attendance!N14="P",5,Attendance!N14="O",3,Attendance!N14="A",0,Attendance!N14="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!N12="P",5,Attendance!N12="O",3,Attendance!N12="A",0,Attendance!N12="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="N14">
-        <f>_xlfn.IFS(Attendance!O14="P",5,Attendance!O14="O",3,Attendance!O14="A",0,Attendance!O14="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!O12="P",5,Attendance!O12="O",3,Attendance!O12="A",0,Attendance!O12="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="O14">
-        <f>_xlfn.IFS(Attendance!P14="P",5,Attendance!P14="O",3,Attendance!P14="A",0,Attendance!P14="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!P12="P",5,Attendance!P12="O",3,Attendance!P12="A",0,Attendance!P12="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="P14">
-        <f>_xlfn.IFS(Attendance!Q14="P",5,Attendance!Q14="O",3,Attendance!Q14="A",0,Attendance!Q14="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!Q12="P",5,Attendance!Q12="O",3,Attendance!Q12="A",0,Attendance!Q12="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="Q14">
-        <f>_xlfn.IFS(Attendance!R14="P",5,Attendance!R14="O",3,Attendance!R14="A",0,Attendance!R14="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!R12="P",5,Attendance!R12="O",3,Attendance!R12="A",0,Attendance!R12="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="R14">
@@ -2439,67 +2369,67 @@
         <v>8</v>
       </c>
       <c r="B15">
-        <f>_xlfn.IFS(Attendance!C15="P",5,Attendance!C15="O",3,Attendance!C15="A",0,Attendance!C15="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!C13="P",5,Attendance!C13="O",3,Attendance!C13="A",0,Attendance!C13="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="C15">
-        <f>_xlfn.IFS(Attendance!D15="P",5,Attendance!D15="O",3,Attendance!D15="A",0,Attendance!D15="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!D13="P",5,Attendance!D13="O",3,Attendance!D13="A",0,Attendance!D13="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="D15">
-        <f>_xlfn.IFS(Attendance!E15="P",5,Attendance!E15="O",3,Attendance!E15="A",0,Attendance!E15="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!E13="P",5,Attendance!E13="O",3,Attendance!E13="A",0,Attendance!E13="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="E15">
-        <f>_xlfn.IFS(Attendance!F15="P",5,Attendance!F15="O",3,Attendance!F15="A",0,Attendance!F15="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!F13="P",5,Attendance!F13="O",3,Attendance!F13="A",0,Attendance!F13="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="F15">
-        <f>_xlfn.IFS(Attendance!G15="P",5,Attendance!G15="O",3,Attendance!G15="A",0,Attendance!G15="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!G13="P",5,Attendance!G13="O",3,Attendance!G13="A",0,Attendance!G13="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="G15">
-        <f>_xlfn.IFS(Attendance!H15="P",5,Attendance!H15="O",3,Attendance!H15="A",0,Attendance!H15="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!H13="P",5,Attendance!H13="O",3,Attendance!H13="A",0,Attendance!H13="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="H15">
-        <f>_xlfn.IFS(Attendance!I15="P",5,Attendance!I15="O",3,Attendance!I15="A",0,Attendance!I15="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!I13="P",5,Attendance!I13="O",3,Attendance!I13="A",0,Attendance!I13="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="I15">
-        <f>_xlfn.IFS(Attendance!J15="P",5,Attendance!J15="O",3,Attendance!J15="A",0,Attendance!J15="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!J13="P",5,Attendance!J13="O",3,Attendance!J13="A",0,Attendance!J13="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="J15">
-        <f>_xlfn.IFS(Attendance!K15="P",5,Attendance!K15="O",3,Attendance!K15="A",0,Attendance!K15="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!K13="P",5,Attendance!K13="O",3,Attendance!K13="A",0,Attendance!K13="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="K15">
-        <f>_xlfn.IFS(Attendance!L15="P",5,Attendance!L15="O",3,Attendance!L15="A",0,Attendance!L15="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!L13="P",5,Attendance!L13="O",3,Attendance!L13="A",0,Attendance!L13="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="L15">
-        <f>_xlfn.IFS(Attendance!M15="P",5,Attendance!M15="O",3,Attendance!M15="A",0,Attendance!M15="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!M13="P",5,Attendance!M13="O",3,Attendance!M13="A",0,Attendance!M13="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="M15">
-        <f>_xlfn.IFS(Attendance!N15="P",5,Attendance!N15="O",3,Attendance!N15="A",0,Attendance!N15="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!N13="P",5,Attendance!N13="O",3,Attendance!N13="A",0,Attendance!N13="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="N15">
-        <f>_xlfn.IFS(Attendance!O15="P",5,Attendance!O15="O",3,Attendance!O15="A",0,Attendance!O15="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!O13="P",5,Attendance!O13="O",3,Attendance!O13="A",0,Attendance!O13="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="O15">
-        <f>_xlfn.IFS(Attendance!P15="P",5,Attendance!P15="O",3,Attendance!P15="A",0,Attendance!P15="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!P13="P",5,Attendance!P13="O",3,Attendance!P13="A",0,Attendance!P13="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="P15">
-        <f>_xlfn.IFS(Attendance!Q15="P",5,Attendance!Q15="O",3,Attendance!Q15="A",0,Attendance!Q15="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!Q13="P",5,Attendance!Q13="O",3,Attendance!Q13="A",0,Attendance!Q13="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="Q15">
-        <f>_xlfn.IFS(Attendance!R15="P",5,Attendance!R15="O",3,Attendance!R15="A",0,Attendance!R15="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!R13="P",5,Attendance!R13="O",3,Attendance!R13="A",0,Attendance!R13="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="R15">
@@ -2516,67 +2446,67 @@
         <v>22</v>
       </c>
       <c r="B16">
-        <f>_xlfn.IFS(Attendance!C16="P",5,Attendance!C16="O",3,Attendance!C16="A",0,Attendance!C16="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!C14="P",5,Attendance!C14="O",3,Attendance!C14="A",0,Attendance!C14="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="C16">
-        <f>_xlfn.IFS(Attendance!D16="P",5,Attendance!D16="O",3,Attendance!D16="A",0,Attendance!D16="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!D14="P",5,Attendance!D14="O",3,Attendance!D14="A",0,Attendance!D14="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="D16">
-        <f>_xlfn.IFS(Attendance!E16="P",5,Attendance!E16="O",3,Attendance!E16="A",0,Attendance!E16="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!E14="P",5,Attendance!E14="O",3,Attendance!E14="A",0,Attendance!E14="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="E16">
-        <f>_xlfn.IFS(Attendance!F16="P",5,Attendance!F16="O",3,Attendance!F16="A",0,Attendance!F16="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!F14="P",5,Attendance!F14="O",3,Attendance!F14="A",0,Attendance!F14="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="F16">
-        <f>_xlfn.IFS(Attendance!G16="P",5,Attendance!G16="O",3,Attendance!G16="A",0,Attendance!G16="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!G14="P",5,Attendance!G14="O",3,Attendance!G14="A",0,Attendance!G14="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="G16">
-        <f>_xlfn.IFS(Attendance!H16="P",5,Attendance!H16="O",3,Attendance!H16="A",0,Attendance!H16="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!H14="P",5,Attendance!H14="O",3,Attendance!H14="A",0,Attendance!H14="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="H16">
-        <f>_xlfn.IFS(Attendance!I16="P",5,Attendance!I16="O",3,Attendance!I16="A",0,Attendance!I16="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!I14="P",5,Attendance!I14="O",3,Attendance!I14="A",0,Attendance!I14="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="I16">
-        <f>_xlfn.IFS(Attendance!J16="P",5,Attendance!J16="O",3,Attendance!J16="A",0,Attendance!J16="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!J14="P",5,Attendance!J14="O",3,Attendance!J14="A",0,Attendance!J14="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="J16">
-        <f>_xlfn.IFS(Attendance!K16="P",5,Attendance!K16="O",3,Attendance!K16="A",0,Attendance!K16="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!K14="P",5,Attendance!K14="O",3,Attendance!K14="A",0,Attendance!K14="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="K16">
-        <f>_xlfn.IFS(Attendance!L16="P",5,Attendance!L16="O",3,Attendance!L16="A",0,Attendance!L16="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!L14="P",5,Attendance!L14="O",3,Attendance!L14="A",0,Attendance!L14="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="L16">
-        <f>_xlfn.IFS(Attendance!M16="P",5,Attendance!M16="O",3,Attendance!M16="A",0,Attendance!M16="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!M14="P",5,Attendance!M14="O",3,Attendance!M14="A",0,Attendance!M14="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="M16">
-        <f>_xlfn.IFS(Attendance!N16="P",5,Attendance!N16="O",3,Attendance!N16="A",0,Attendance!N16="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!N14="P",5,Attendance!N14="O",3,Attendance!N14="A",0,Attendance!N14="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="N16">
-        <f>_xlfn.IFS(Attendance!O16="P",5,Attendance!O16="O",3,Attendance!O16="A",0,Attendance!O16="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!O14="P",5,Attendance!O14="O",3,Attendance!O14="A",0,Attendance!O14="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="O16">
-        <f>_xlfn.IFS(Attendance!P16="P",5,Attendance!P16="O",3,Attendance!P16="A",0,Attendance!P16="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!P14="P",5,Attendance!P14="O",3,Attendance!P14="A",0,Attendance!P14="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="P16">
-        <f>_xlfn.IFS(Attendance!Q16="P",5,Attendance!Q16="O",3,Attendance!Q16="A",0,Attendance!Q16="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!Q14="P",5,Attendance!Q14="O",3,Attendance!Q14="A",0,Attendance!Q14="N/A",0)</f>
         <v>0</v>
       </c>
       <c r="Q16">
-        <f>_xlfn.IFS(Attendance!R16="P",5,Attendance!R16="O",3,Attendance!R16="A",0,Attendance!R16="N/A",0)</f>
+        <f>_xlfn.IFS(Attendance!R14="P",5,Attendance!R14="O",3,Attendance!R14="A",0,Attendance!R14="N/A",0)</f>
         <v>5</v>
       </c>
       <c r="R16">

--- a/24_DS_CLUB_BATCH1_AHM/Attendance.xlsx
+++ b/24_DS_CLUB_BATCH1_AHM/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_CLUB_BATCH1_AHM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B66B1462-FC72-4865-8BC3-D13B41CBB2D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F61FA469-55C9-434C-8520-0ABA3BF9C9BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="25">
   <si>
     <t>Name</t>
   </si>
@@ -453,14 +453,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -518,8 +518,14 @@
       <c r="S1" s="1">
         <v>45613</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T1" s="1">
+        <v>45619</v>
+      </c>
+      <c r="U1" s="1">
+        <v>45620</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -577,8 +583,14 @@
       <c r="S2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -636,8 +648,14 @@
       <c r="S3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T3" t="s">
+        <v>2</v>
+      </c>
+      <c r="U3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -695,8 +713,14 @@
       <c r="S4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T4" t="s">
+        <v>2</v>
+      </c>
+      <c r="U4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -754,8 +778,14 @@
       <c r="S5" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T5" t="s">
+        <v>1</v>
+      </c>
+      <c r="U5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -813,8 +843,14 @@
       <c r="S6" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T6" t="s">
+        <v>3</v>
+      </c>
+      <c r="U6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -872,8 +908,14 @@
       <c r="S7" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T7" t="s">
+        <v>2</v>
+      </c>
+      <c r="U7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -931,8 +973,14 @@
       <c r="S8" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T8" t="s">
+        <v>2</v>
+      </c>
+      <c r="U8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -990,8 +1038,14 @@
       <c r="S9" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T9" t="s">
+        <v>2</v>
+      </c>
+      <c r="U9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1049,8 +1103,14 @@
       <c r="S10" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T10" t="s">
+        <v>2</v>
+      </c>
+      <c r="U10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1108,8 +1168,14 @@
       <c r="S11" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T11" t="s">
+        <v>2</v>
+      </c>
+      <c r="U11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -1167,8 +1233,14 @@
       <c r="S12" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T12" t="s">
+        <v>2</v>
+      </c>
+      <c r="U12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -1223,8 +1295,14 @@
       <c r="S13" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T13" t="s">
+        <v>2</v>
+      </c>
+      <c r="U13" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -1282,8 +1360,14 @@
       <c r="S14" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T14" t="s">
+        <v>2</v>
+      </c>
+      <c r="U14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>20</v>
       </c>

--- a/24_DS_CLUB_BATCH1_AHM/Attendance.xlsx
+++ b/24_DS_CLUB_BATCH1_AHM/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_CLUB_BATCH1_AHM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F61FA469-55C9-434C-8520-0ABA3BF9C9BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF3AFC29-85E0-4438-BC92-2EE1D22007BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="25">
   <si>
     <t>Name</t>
   </si>
@@ -453,14 +453,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -524,8 +524,11 @@
       <c r="U1" s="1">
         <v>45620</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V1" s="1">
+        <v>45627</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -589,8 +592,11 @@
       <c r="U2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -654,8 +660,11 @@
       <c r="U3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -719,8 +728,11 @@
       <c r="U4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -784,8 +796,11 @@
       <c r="U5" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -849,8 +864,11 @@
       <c r="U6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -914,8 +932,11 @@
       <c r="U7" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -979,8 +1000,11 @@
       <c r="U8" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1044,8 +1068,11 @@
       <c r="U9" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1109,8 +1136,11 @@
       <c r="U10" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1174,8 +1204,11 @@
       <c r="U11" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -1239,8 +1272,11 @@
       <c r="U12" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V12" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -1301,8 +1337,11 @@
       <c r="U13" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V13" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -1358,16 +1397,19 @@
         <v>1</v>
       </c>
       <c r="S14" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="T14" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="U14" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="V14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>20</v>
       </c>

--- a/24_DS_CLUB_BATCH1_AHM/Attendance.xlsx
+++ b/24_DS_CLUB_BATCH1_AHM/Attendance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_CLUB_BATCH1_AHM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF3AFC29-85E0-4438-BC92-2EE1D22007BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95EF2753-9829-4C79-B46E-8E7416AE9DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="25">
   <si>
     <t>Name</t>
   </si>
@@ -453,14 +453,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:Y16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -527,8 +527,17 @@
       <c r="V1" s="1">
         <v>45627</v>
       </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W1" s="1">
+        <v>45634</v>
+      </c>
+      <c r="X1" s="1">
+        <v>45640</v>
+      </c>
+      <c r="Y1" s="1">
+        <v>45647</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -595,8 +604,14 @@
       <c r="V2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -663,8 +678,14 @@
       <c r="V3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X3" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -731,8 +752,17 @@
       <c r="V4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W4" t="s">
+        <v>1</v>
+      </c>
+      <c r="X4" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -799,8 +829,14 @@
       <c r="V5" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X5" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -867,8 +903,14 @@
       <c r="V6" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X6" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -935,8 +977,14 @@
       <c r="V7" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X7" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1003,8 +1051,14 @@
       <c r="V8" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X8" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1071,8 +1125,14 @@
       <c r="V9" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X9" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1139,8 +1199,14 @@
       <c r="V10" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X10" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1207,8 +1273,14 @@
       <c r="V11" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X11" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -1275,8 +1347,14 @@
       <c r="V12" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X12" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -1340,8 +1418,14 @@
       <c r="V13" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X13" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -1408,8 +1492,14 @@
       <c r="V14" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X14" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>20</v>
       </c>

--- a/24_DS_CLUB_BATCH1_AHM/Attendance.xlsx
+++ b/24_DS_CLUB_BATCH1_AHM/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_CLUB_BATCH1_AHM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95EF2753-9829-4C79-B46E-8E7416AE9DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D42583B5-D6B6-4A67-BD49-0D73872503F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="26">
   <si>
     <t>Name</t>
   </si>
@@ -101,6 +101,9 @@
   </si>
   <si>
     <t>Total/5</t>
+  </si>
+  <si>
+    <t>Krushna Raval</t>
   </si>
 </sst>
 </file>
@@ -453,14 +456,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:Y16"/>
+  <dimension ref="A1:AB17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -536,8 +539,17 @@
       <c r="Y1" s="1">
         <v>45647</v>
       </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z1" s="1">
+        <v>46020</v>
+      </c>
+      <c r="AA1" s="1">
+        <v>45662</v>
+      </c>
+      <c r="AB1" s="1">
+        <v>45669</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -610,8 +622,11 @@
       <c r="Y2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AB2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -684,8 +699,11 @@
       <c r="Y3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AB3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -761,8 +779,11 @@
       <c r="Y4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AB4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -835,8 +856,11 @@
       <c r="Y5" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AB5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -909,8 +933,11 @@
       <c r="Y6" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AB6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -983,8 +1010,11 @@
       <c r="Y7" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AB7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1057,8 +1087,11 @@
       <c r="Y8" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AB8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1131,8 +1164,11 @@
       <c r="Y9" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AB9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1205,8 +1241,11 @@
       <c r="Y10" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AB10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1279,8 +1318,11 @@
       <c r="Y11" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AB11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -1353,8 +1395,11 @@
       <c r="Y12" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AB12" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -1424,8 +1469,11 @@
       <c r="Y13" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AB13" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -1498,9 +1546,98 @@
       <c r="Y14" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="AB14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" t="s">
+        <v>12</v>
+      </c>
+      <c r="I15" t="s">
+        <v>12</v>
+      </c>
+      <c r="J15" t="s">
+        <v>12</v>
+      </c>
+      <c r="K15" t="s">
+        <v>12</v>
+      </c>
+      <c r="L15" t="s">
+        <v>12</v>
+      </c>
+      <c r="M15" t="s">
+        <v>12</v>
+      </c>
+      <c r="N15" t="s">
+        <v>12</v>
+      </c>
+      <c r="O15" t="s">
+        <v>12</v>
+      </c>
+      <c r="P15" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>12</v>
+      </c>
+      <c r="R15" t="s">
+        <v>12</v>
+      </c>
+      <c r="S15" t="s">
+        <v>12</v>
+      </c>
+      <c r="T15" t="s">
+        <v>12</v>
+      </c>
+      <c r="U15" t="s">
+        <v>12</v>
+      </c>
+      <c r="V15" t="s">
+        <v>12</v>
+      </c>
+      <c r="W15" t="s">
+        <v>12</v>
+      </c>
+      <c r="X15" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>20</v>
       </c>
     </row>

--- a/24_DS_CLUB_BATCH1_AHM/Attendance.xlsx
+++ b/24_DS_CLUB_BATCH1_AHM/Attendance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_CLUB_BATCH1_AHM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D42583B5-D6B6-4A67-BD49-0D73872503F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05BA422B-6054-4A64-A248-1465246E5562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="26">
   <si>
     <t>Name</t>
   </si>
@@ -456,14 +456,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:AB17"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -548,8 +548,11 @@
       <c r="AB1" s="1">
         <v>45669</v>
       </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AC1" s="1">
+        <v>45676</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -625,8 +628,11 @@
       <c r="AB2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AC2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -702,8 +708,11 @@
       <c r="AB3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AC3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -782,8 +791,11 @@
       <c r="AB4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AC4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -859,8 +871,11 @@
       <c r="AB5" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AC5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -936,8 +951,11 @@
       <c r="AB6" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AC6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1013,8 +1031,11 @@
       <c r="AB7" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AC7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1090,8 +1111,11 @@
       <c r="AB8" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AC8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1167,8 +1191,11 @@
       <c r="AB9" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AC9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1244,8 +1271,11 @@
       <c r="AB10" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AC10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1321,8 +1351,11 @@
       <c r="AB11" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AC11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -1398,8 +1431,11 @@
       <c r="AB12" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AC12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -1472,8 +1508,11 @@
       <c r="AB13" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AC13" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -1549,8 +1588,11 @@
       <c r="AB14" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AC14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -1633,6 +1675,9 @@
         <v>12</v>
       </c>
       <c r="AB15" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC15" t="s">
         <v>1</v>
       </c>
     </row>

--- a/24_DS_CLUB_BATCH1_AHM/Attendance.xlsx
+++ b/24_DS_CLUB_BATCH1_AHM/Attendance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_CLUB_BATCH1_AHM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05BA422B-6054-4A64-A248-1465246E5562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB8F1D05-C42B-4AD0-9613-17F6B371EE21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="26">
   <si>
     <t>Name</t>
   </si>
@@ -456,14 +456,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AE17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -551,8 +551,11 @@
       <c r="AC1" s="1">
         <v>45676</v>
       </c>
-    </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AE1" s="1">
+        <v>45725</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -631,8 +634,11 @@
       <c r="AC2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AE2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -711,8 +717,11 @@
       <c r="AC3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AE3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -794,8 +803,11 @@
       <c r="AC4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AE4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -874,8 +886,11 @@
       <c r="AC5" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AE5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -954,8 +969,11 @@
       <c r="AC6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AE6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1034,8 +1052,11 @@
       <c r="AC7" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AE7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1114,8 +1135,11 @@
       <c r="AC8" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AE8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1194,8 +1218,11 @@
       <c r="AC9" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AE9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1274,8 +1301,11 @@
       <c r="AC10" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AE10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1354,8 +1384,11 @@
       <c r="AC11" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AE11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -1434,8 +1467,11 @@
       <c r="AC12" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AE12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -1511,8 +1547,11 @@
       <c r="AC13" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AE13" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -1591,8 +1630,11 @@
       <c r="AC14" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AE14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -1679,6 +1721,9 @@
       </c>
       <c r="AC15" t="s">
         <v>1</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">

--- a/24_DS_CLUB_BATCH1_AHM/Attendance.xlsx
+++ b/24_DS_CLUB_BATCH1_AHM/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_CLUB_BATCH1_AHM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB8F1D05-C42B-4AD0-9613-17F6B371EE21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6E9F194-25E3-488C-80BE-1EE8250A43AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Attendance" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Attendance!$A$1:$AG$25</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -26,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="36">
   <si>
     <t>Name</t>
   </si>
@@ -88,9 +91,6 @@
     <t>Parth Thakkar</t>
   </si>
   <si>
-    <t>Count of students</t>
-  </si>
-  <si>
     <t>Jalp Panchal</t>
   </si>
   <si>
@@ -104,6 +104,39 @@
   </si>
   <si>
     <t>Krushna Raval</t>
+  </si>
+  <si>
+    <t>Agnivesh Patel</t>
+  </si>
+  <si>
+    <t>Dev Bhatt</t>
+  </si>
+  <si>
+    <t>Harit Pansuriya</t>
+  </si>
+  <si>
+    <t>Kashish Patel</t>
+  </si>
+  <si>
+    <t>Khush Mevada</t>
+  </si>
+  <si>
+    <t>Mosam Patel</t>
+  </si>
+  <si>
+    <t>Yesha Chaudhary</t>
+  </si>
+  <si>
+    <t>Ved Nayi</t>
+  </si>
+  <si>
+    <t>Vishwa</t>
+  </si>
+  <si>
+    <t>Diya</t>
+  </si>
+  <si>
+    <t>Yash Chauhan</t>
   </si>
 </sst>
 </file>
@@ -139,9 +172,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -456,108 +495,124 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:AE17"/>
+  <dimension ref="A1:AG26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.44140625" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="18" width="11" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="31" max="33" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:33" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="1">
+      <c r="C1" s="3">
         <v>45424</v>
       </c>
-      <c r="D1" s="1">
+      <c r="D1" s="3">
         <v>45431</v>
       </c>
-      <c r="E1" s="1">
+      <c r="E1" s="3">
         <v>45438</v>
       </c>
-      <c r="F1" s="1">
+      <c r="F1" s="3">
         <v>45445</v>
       </c>
-      <c r="G1" s="1">
+      <c r="G1" s="3">
         <v>45459</v>
       </c>
-      <c r="H1" s="1">
+      <c r="H1" s="3">
         <v>45466</v>
       </c>
-      <c r="I1" s="1">
+      <c r="I1" s="3">
         <v>45473</v>
       </c>
-      <c r="J1" s="1">
+      <c r="J1" s="3">
         <v>45487</v>
       </c>
-      <c r="K1" s="1">
+      <c r="K1" s="3">
         <v>45494</v>
       </c>
-      <c r="L1" s="1">
+      <c r="L1" s="3">
         <v>45522</v>
       </c>
-      <c r="M1" s="1">
+      <c r="M1" s="3">
         <v>45529</v>
       </c>
-      <c r="N1" s="1">
+      <c r="N1" s="3">
         <v>45536</v>
       </c>
-      <c r="O1" s="1">
+      <c r="O1" s="3">
         <v>45543</v>
       </c>
-      <c r="P1" s="1">
+      <c r="P1" s="3">
         <v>45550</v>
       </c>
-      <c r="Q1" s="1">
+      <c r="Q1" s="3">
         <v>45557</v>
       </c>
-      <c r="R1" s="1">
+      <c r="R1" s="3">
         <v>45578</v>
       </c>
-      <c r="S1" s="1">
+      <c r="S1" s="3">
         <v>45613</v>
       </c>
-      <c r="T1" s="1">
+      <c r="T1" s="3">
         <v>45619</v>
       </c>
-      <c r="U1" s="1">
+      <c r="U1" s="3">
         <v>45620</v>
       </c>
-      <c r="V1" s="1">
+      <c r="V1" s="3">
         <v>45627</v>
       </c>
-      <c r="W1" s="1">
+      <c r="W1" s="3">
         <v>45634</v>
       </c>
-      <c r="X1" s="1">
+      <c r="X1" s="3">
         <v>45640</v>
       </c>
-      <c r="Y1" s="1">
+      <c r="Y1" s="3">
         <v>45647</v>
       </c>
-      <c r="Z1" s="1">
+      <c r="Z1" s="3">
         <v>46020</v>
       </c>
-      <c r="AA1" s="1">
+      <c r="AA1" s="3">
         <v>45662</v>
       </c>
-      <c r="AB1" s="1">
+      <c r="AB1" s="3">
         <v>45669</v>
       </c>
-      <c r="AC1" s="1">
+      <c r="AC1" s="3">
         <v>45676</v>
       </c>
-      <c r="AE1" s="1">
+      <c r="AD1" s="3"/>
+      <c r="AE1" s="3">
         <v>45725</v>
       </c>
-    </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF1" s="3">
+        <v>45739</v>
+      </c>
+      <c r="AG1" s="3">
+        <v>45746</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
@@ -593,34 +648,34 @@
         <v>12</v>
       </c>
       <c r="M2" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="N2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O2" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="P2" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="Q2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="R2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S2" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="T2" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="U2" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="V2" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="X2" t="s">
         <v>1</v>
@@ -635,481 +690,202 @@
         <v>1</v>
       </c>
       <c r="AE2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K3" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" t="s">
-        <v>1</v>
-      </c>
-      <c r="M3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>1</v>
-      </c>
-      <c r="R3" t="s">
-        <v>1</v>
-      </c>
-      <c r="S3" t="s">
-        <v>2</v>
-      </c>
-      <c r="T3" t="s">
-        <v>2</v>
-      </c>
-      <c r="U3" t="s">
-        <v>2</v>
-      </c>
-      <c r="V3" t="s">
-        <v>1</v>
-      </c>
-      <c r="X3" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4" t="s">
-        <v>3</v>
-      </c>
-      <c r="K4" t="s">
-        <v>3</v>
-      </c>
-      <c r="L4" t="s">
-        <v>1</v>
-      </c>
-      <c r="M4" t="s">
-        <v>1</v>
-      </c>
-      <c r="N4" t="s">
-        <v>1</v>
-      </c>
-      <c r="O4" t="s">
-        <v>1</v>
-      </c>
-      <c r="P4" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>1</v>
-      </c>
-      <c r="R4" t="s">
-        <v>3</v>
-      </c>
-      <c r="S4" t="s">
-        <v>1</v>
-      </c>
-      <c r="T4" t="s">
-        <v>2</v>
-      </c>
-      <c r="U4" t="s">
-        <v>1</v>
-      </c>
-      <c r="V4" t="s">
-        <v>1</v>
-      </c>
-      <c r="W4" t="s">
-        <v>1</v>
-      </c>
-      <c r="X4" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>2</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G5" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" t="s">
-        <v>1</v>
-      </c>
-      <c r="J5" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" t="s">
-        <v>1</v>
-      </c>
-      <c r="L5" t="s">
-        <v>1</v>
-      </c>
-      <c r="M5" t="s">
-        <v>3</v>
-      </c>
-      <c r="N5" t="s">
-        <v>1</v>
-      </c>
-      <c r="O5" t="s">
-        <v>1</v>
-      </c>
-      <c r="P5" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>3</v>
-      </c>
-      <c r="R5" t="s">
-        <v>3</v>
-      </c>
-      <c r="S5" t="s">
-        <v>1</v>
-      </c>
-      <c r="T5" t="s">
-        <v>1</v>
-      </c>
-      <c r="U5" t="s">
-        <v>1</v>
-      </c>
-      <c r="V5" t="s">
-        <v>1</v>
-      </c>
-      <c r="X5" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" t="s">
-        <v>2</v>
-      </c>
-      <c r="F6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G6" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" t="s">
-        <v>1</v>
-      </c>
-      <c r="L6" t="s">
-        <v>1</v>
-      </c>
-      <c r="M6" t="s">
-        <v>1</v>
-      </c>
-      <c r="N6" t="s">
-        <v>3</v>
-      </c>
-      <c r="O6" t="s">
-        <v>1</v>
-      </c>
-      <c r="P6" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>1</v>
-      </c>
-      <c r="R6" t="s">
-        <v>1</v>
-      </c>
-      <c r="S6" t="s">
-        <v>1</v>
-      </c>
-      <c r="T6" t="s">
-        <v>3</v>
-      </c>
-      <c r="U6" t="s">
-        <v>3</v>
-      </c>
-      <c r="V6" t="s">
-        <v>1</v>
-      </c>
-      <c r="X6" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H7" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I7" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J7" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K7" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="L7" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="M7" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N7" t="s">
         <v>3</v>
       </c>
       <c r="O7" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X7" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC7" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H8" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I8" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J8" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N8" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O8" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P8" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S8" t="s">
         <v>2</v>
@@ -1121,27 +897,33 @@
         <v>2</v>
       </c>
       <c r="V8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="s">
         <v>2</v>
       </c>
       <c r="AB8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC8" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF8" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
@@ -1159,19 +941,19 @@
         <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H9" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="I9" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J9" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K9" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L9" t="s">
         <v>1</v>
@@ -1183,300 +965,174 @@
         <v>1</v>
       </c>
       <c r="O9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R9" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T9" t="s">
         <v>2</v>
       </c>
       <c r="U9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V9" t="s">
         <v>1</v>
       </c>
+      <c r="W9" t="s">
+        <v>1</v>
+      </c>
       <c r="X9" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="s">
         <v>2</v>
       </c>
       <c r="AB9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC9" t="s">
         <v>2</v>
       </c>
       <c r="AE9" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" t="s">
-        <v>1</v>
-      </c>
-      <c r="G10" t="s">
-        <v>2</v>
-      </c>
-      <c r="H10" t="s">
-        <v>1</v>
-      </c>
-      <c r="I10" t="s">
-        <v>2</v>
-      </c>
-      <c r="J10" t="s">
-        <v>2</v>
-      </c>
-      <c r="K10" t="s">
-        <v>2</v>
-      </c>
-      <c r="L10" t="s">
-        <v>2</v>
-      </c>
-      <c r="M10" t="s">
-        <v>2</v>
-      </c>
-      <c r="N10" t="s">
-        <v>2</v>
-      </c>
-      <c r="O10" t="s">
-        <v>2</v>
-      </c>
-      <c r="P10" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>2</v>
-      </c>
-      <c r="R10" t="s">
-        <v>2</v>
-      </c>
-      <c r="S10" t="s">
-        <v>2</v>
-      </c>
-      <c r="T10" t="s">
-        <v>2</v>
-      </c>
-      <c r="U10" t="s">
-        <v>2</v>
-      </c>
-      <c r="V10" t="s">
-        <v>2</v>
-      </c>
-      <c r="X10" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>2</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11" t="s">
         <v>2</v>
       </c>
       <c r="G11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M11" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R11" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE11" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s">
         <v>15</v>
       </c>
-      <c r="C12" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" t="s">
-        <v>2</v>
-      </c>
-      <c r="E12" t="s">
-        <v>2</v>
-      </c>
-      <c r="F12" t="s">
-        <v>1</v>
-      </c>
-      <c r="G12" t="s">
-        <v>2</v>
-      </c>
-      <c r="H12" t="s">
-        <v>2</v>
-      </c>
-      <c r="I12" t="s">
-        <v>1</v>
-      </c>
-      <c r="J12" t="s">
-        <v>2</v>
-      </c>
-      <c r="K12" t="s">
-        <v>1</v>
-      </c>
-      <c r="L12" t="s">
-        <v>1</v>
-      </c>
-      <c r="M12" t="s">
-        <v>3</v>
-      </c>
-      <c r="N12" t="s">
-        <v>1</v>
-      </c>
-      <c r="O12" t="s">
-        <v>1</v>
-      </c>
-      <c r="P12" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>2</v>
-      </c>
-      <c r="R12" t="s">
-        <v>1</v>
-      </c>
-      <c r="S12" t="s">
-        <v>2</v>
-      </c>
-      <c r="T12" t="s">
-        <v>2</v>
-      </c>
-      <c r="U12" t="s">
-        <v>2</v>
-      </c>
-      <c r="V12" t="s">
-        <v>1</v>
-      </c>
-      <c r="X12" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB12" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
       <c r="C13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="s">
         <v>2</v>
@@ -1488,155 +1144,167 @@
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N13" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T13" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U13" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC13" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE13" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D14" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E14" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G14" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H14" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="I14" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K14" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L14" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M14" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="N14" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="O14" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="P14" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="R14" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S14" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="T14" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="U14" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="V14" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="X14" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
         <v>15</v>
@@ -1725,13 +1393,605 @@
       <c r="AE15" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="AF15" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>9</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E17" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I17" t="s">
+        <v>2</v>
+      </c>
+      <c r="J17" t="s">
+        <v>2</v>
+      </c>
+      <c r="K17" t="s">
+        <v>2</v>
+      </c>
+      <c r="L17" t="s">
+        <v>2</v>
+      </c>
+      <c r="M17" t="s">
+        <v>2</v>
+      </c>
+      <c r="N17" t="s">
+        <v>2</v>
+      </c>
+      <c r="O17" t="s">
+        <v>2</v>
+      </c>
+      <c r="P17" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>2</v>
+      </c>
+      <c r="R17" t="s">
+        <v>2</v>
+      </c>
+      <c r="S17" t="s">
+        <v>2</v>
+      </c>
+      <c r="T17" t="s">
+        <v>2</v>
+      </c>
+      <c r="U17" t="s">
+        <v>2</v>
+      </c>
+      <c r="V17" t="s">
+        <v>2</v>
+      </c>
+      <c r="X17" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>2</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>2</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" t="s">
+        <v>12</v>
+      </c>
+      <c r="I18" t="s">
+        <v>12</v>
+      </c>
+      <c r="J18" t="s">
+        <v>1</v>
+      </c>
+      <c r="K18" t="s">
+        <v>1</v>
+      </c>
+      <c r="L18" t="s">
+        <v>1</v>
+      </c>
+      <c r="M18" t="s">
+        <v>1</v>
+      </c>
+      <c r="N18" t="s">
+        <v>1</v>
+      </c>
+      <c r="O18" t="s">
+        <v>2</v>
+      </c>
+      <c r="P18" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>2</v>
+      </c>
+      <c r="R18" t="s">
+        <v>2</v>
+      </c>
+      <c r="S18" t="s">
+        <v>2</v>
+      </c>
+      <c r="T18" t="s">
+        <v>2</v>
+      </c>
+      <c r="U18" t="s">
+        <v>2</v>
+      </c>
+      <c r="V18" t="s">
+        <v>1</v>
+      </c>
+      <c r="X18" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>2</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>2</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" t="s">
+        <v>3</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" t="s">
+        <v>1</v>
+      </c>
+      <c r="G19" t="s">
+        <v>2</v>
+      </c>
+      <c r="H19" t="s">
+        <v>1</v>
+      </c>
+      <c r="I19" t="s">
+        <v>2</v>
+      </c>
+      <c r="J19" t="s">
+        <v>2</v>
+      </c>
+      <c r="K19" t="s">
+        <v>2</v>
+      </c>
+      <c r="L19" t="s">
+        <v>2</v>
+      </c>
+      <c r="M19" t="s">
+        <v>2</v>
+      </c>
+      <c r="N19" t="s">
+        <v>2</v>
+      </c>
+      <c r="O19" t="s">
+        <v>2</v>
+      </c>
+      <c r="P19" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>2</v>
+      </c>
+      <c r="R19" t="s">
+        <v>2</v>
+      </c>
+      <c r="S19" t="s">
+        <v>2</v>
+      </c>
+      <c r="T19" t="s">
+        <v>2</v>
+      </c>
+      <c r="U19" t="s">
+        <v>2</v>
+      </c>
+      <c r="V19" t="s">
+        <v>2</v>
+      </c>
+      <c r="X19" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>2</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>2</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" t="s">
+        <v>2</v>
+      </c>
+      <c r="G20" t="s">
+        <v>2</v>
+      </c>
+      <c r="H20" t="s">
+        <v>2</v>
+      </c>
+      <c r="I20" t="s">
+        <v>2</v>
+      </c>
+      <c r="J20" t="s">
+        <v>2</v>
+      </c>
+      <c r="K20" t="s">
+        <v>2</v>
+      </c>
+      <c r="L20" t="s">
+        <v>2</v>
+      </c>
+      <c r="M20" t="s">
+        <v>2</v>
+      </c>
+      <c r="N20" t="s">
+        <v>2</v>
+      </c>
+      <c r="O20" t="s">
+        <v>2</v>
+      </c>
+      <c r="P20" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>2</v>
+      </c>
+      <c r="R20" t="s">
+        <v>2</v>
+      </c>
+      <c r="S20" t="s">
+        <v>2</v>
+      </c>
+      <c r="T20" t="s">
+        <v>2</v>
+      </c>
+      <c r="U20" t="s">
+        <v>2</v>
+      </c>
+      <c r="V20" t="s">
+        <v>2</v>
+      </c>
+      <c r="X20" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>2</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>2</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG20" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1</v>
+      </c>
+      <c r="D21" t="s">
+        <v>2</v>
+      </c>
+      <c r="E21" t="s">
+        <v>2</v>
+      </c>
+      <c r="F21" t="s">
+        <v>1</v>
+      </c>
+      <c r="G21" t="s">
+        <v>2</v>
+      </c>
+      <c r="H21" t="s">
+        <v>2</v>
+      </c>
+      <c r="I21" t="s">
+        <v>1</v>
+      </c>
+      <c r="J21" t="s">
+        <v>2</v>
+      </c>
+      <c r="K21" t="s">
+        <v>1</v>
+      </c>
+      <c r="L21" t="s">
+        <v>1</v>
+      </c>
+      <c r="M21" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" t="s">
+        <v>1</v>
+      </c>
+      <c r="O21" t="s">
+        <v>1</v>
+      </c>
+      <c r="P21" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>2</v>
+      </c>
+      <c r="R21" t="s">
+        <v>1</v>
+      </c>
+      <c r="S21" t="s">
+        <v>2</v>
+      </c>
+      <c r="T21" t="s">
+        <v>2</v>
+      </c>
+      <c r="U21" t="s">
+        <v>2</v>
+      </c>
+      <c r="V21" t="s">
+        <v>1</v>
+      </c>
+      <c r="X21" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>2</v>
+      </c>
+      <c r="AF21" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF22" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG22" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" t="s">
+        <v>2</v>
+      </c>
+      <c r="E23" t="s">
+        <v>2</v>
+      </c>
+      <c r="F23" t="s">
+        <v>2</v>
+      </c>
+      <c r="G23" t="s">
+        <v>2</v>
+      </c>
+      <c r="H23" t="s">
+        <v>2</v>
+      </c>
+      <c r="I23" t="s">
+        <v>2</v>
+      </c>
+      <c r="J23" t="s">
+        <v>2</v>
+      </c>
+      <c r="K23" t="s">
+        <v>2</v>
+      </c>
+      <c r="L23" t="s">
+        <v>2</v>
+      </c>
+      <c r="M23" t="s">
+        <v>2</v>
+      </c>
+      <c r="N23" t="s">
+        <v>2</v>
+      </c>
+      <c r="O23" t="s">
+        <v>2</v>
+      </c>
+      <c r="P23" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>2</v>
+      </c>
+      <c r="R23" t="s">
+        <v>2</v>
+      </c>
+      <c r="S23" t="s">
+        <v>2</v>
+      </c>
+      <c r="T23" t="s">
+        <v>2</v>
+      </c>
+      <c r="U23" t="s">
+        <v>2</v>
+      </c>
+      <c r="V23" t="s">
+        <v>2</v>
+      </c>
+      <c r="X23" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>2</v>
+      </c>
+      <c r="AE23" t="s">
+        <v>2</v>
+      </c>
+      <c r="AF23" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG23" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF24" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG24" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF25" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG25" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF26" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG26" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AG25" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AG25">
+      <sortCondition ref="A1:A25"/>
+    </sortState>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O13">
     <sortCondition ref="A2:A13"/>
   </sortState>
@@ -1800,10 +2060,10 @@
         <v>45578</v>
       </c>
       <c r="R1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S1" t="s">
         <v>23</v>
-      </c>
-      <c r="S1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
@@ -1852,117 +2112,117 @@
       </c>
       <c r="L2">
         <f>_xlfn.IFS(Attendance!M2="P",5,Attendance!M2="O",3,Attendance!M2="A",0,Attendance!M2="N/A",0)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M2">
         <f>_xlfn.IFS(Attendance!N2="P",5,Attendance!N2="O",3,Attendance!N2="A",0,Attendance!N2="N/A",0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N2">
         <f>_xlfn.IFS(Attendance!O2="P",5,Attendance!O2="O",3,Attendance!O2="A",0,Attendance!O2="N/A",0)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O2">
         <f>_xlfn.IFS(Attendance!P2="P",5,Attendance!P2="O",3,Attendance!P2="A",0,Attendance!P2="N/A",0)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <f>_xlfn.IFS(Attendance!Q2="P",5,Attendance!Q2="O",3,Attendance!Q2="A",0,Attendance!Q2="N/A",0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q2">
         <f>_xlfn.IFS(Attendance!R2="P",5,Attendance!R2="O",3,Attendance!R2="A",0,Attendance!R2="N/A",0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R2">
         <f>SUM(B2:Q2)</f>
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="S2">
         <f>ROUND(R2*5/80, 2)</f>
-        <v>1.31</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="e">
         <f>_xlfn.IFS(Attendance!C3="P",5,Attendance!C3="O",3,Attendance!C3="A",0,Attendance!C3="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="C3">
+        <v>#N/A</v>
+      </c>
+      <c r="C3" t="e">
         <f>_xlfn.IFS(Attendance!D3="P",5,Attendance!D3="O",3,Attendance!D3="A",0,Attendance!D3="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="D3">
+        <v>#N/A</v>
+      </c>
+      <c r="D3" t="e">
         <f>_xlfn.IFS(Attendance!E3="P",5,Attendance!E3="O",3,Attendance!E3="A",0,Attendance!E3="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="E3">
+        <v>#N/A</v>
+      </c>
+      <c r="E3" t="e">
         <f>_xlfn.IFS(Attendance!F3="P",5,Attendance!F3="O",3,Attendance!F3="A",0,Attendance!F3="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="F3">
+        <v>#N/A</v>
+      </c>
+      <c r="F3" t="e">
         <f>_xlfn.IFS(Attendance!G3="P",5,Attendance!G3="O",3,Attendance!G3="A",0,Attendance!G3="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="G3">
+        <v>#N/A</v>
+      </c>
+      <c r="G3" t="e">
         <f>_xlfn.IFS(Attendance!H3="P",5,Attendance!H3="O",3,Attendance!H3="A",0,Attendance!H3="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="H3">
+        <v>#N/A</v>
+      </c>
+      <c r="H3" t="e">
         <f>_xlfn.IFS(Attendance!I3="P",5,Attendance!I3="O",3,Attendance!I3="A",0,Attendance!I3="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="I3">
+        <v>#N/A</v>
+      </c>
+      <c r="I3" t="e">
         <f>_xlfn.IFS(Attendance!J3="P",5,Attendance!J3="O",3,Attendance!J3="A",0,Attendance!J3="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="J3">
+        <v>#N/A</v>
+      </c>
+      <c r="J3" t="e">
         <f>_xlfn.IFS(Attendance!K3="P",5,Attendance!K3="O",3,Attendance!K3="A",0,Attendance!K3="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="K3">
+        <v>#N/A</v>
+      </c>
+      <c r="K3" t="e">
         <f>_xlfn.IFS(Attendance!L3="P",5,Attendance!L3="O",3,Attendance!L3="A",0,Attendance!L3="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="L3">
+        <v>#N/A</v>
+      </c>
+      <c r="L3" t="e">
         <f>_xlfn.IFS(Attendance!M3="P",5,Attendance!M3="O",3,Attendance!M3="A",0,Attendance!M3="N/A",0)</f>
-        <v>3</v>
-      </c>
-      <c r="M3">
+        <v>#N/A</v>
+      </c>
+      <c r="M3" t="e">
         <f>_xlfn.IFS(Attendance!N3="P",5,Attendance!N3="O",3,Attendance!N3="A",0,Attendance!N3="N/A",0)</f>
-        <v>3</v>
-      </c>
-      <c r="N3">
+        <v>#N/A</v>
+      </c>
+      <c r="N3" t="e">
         <f>_xlfn.IFS(Attendance!O3="P",5,Attendance!O3="O",3,Attendance!O3="A",0,Attendance!O3="N/A",0)</f>
-        <v>3</v>
-      </c>
-      <c r="O3">
+        <v>#N/A</v>
+      </c>
+      <c r="O3" t="e">
         <f>_xlfn.IFS(Attendance!P3="P",5,Attendance!P3="O",3,Attendance!P3="A",0,Attendance!P3="N/A",0)</f>
-        <v>3</v>
-      </c>
-      <c r="P3">
+        <v>#N/A</v>
+      </c>
+      <c r="P3" t="e">
         <f>_xlfn.IFS(Attendance!Q3="P",5,Attendance!Q3="O",3,Attendance!Q3="A",0,Attendance!Q3="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="Q3">
+        <v>#N/A</v>
+      </c>
+      <c r="Q3" t="e">
         <f>_xlfn.IFS(Attendance!R3="P",5,Attendance!R3="O",3,Attendance!R3="A",0,Attendance!R3="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="R3">
+        <v>#N/A</v>
+      </c>
+      <c r="R3" t="e">
         <f t="shared" ref="R3:R16" si="0">SUM(B3:Q3)</f>
-        <v>32</v>
-      </c>
-      <c r="S3">
+        <v>#N/A</v>
+      </c>
+      <c r="S3" t="e">
         <f t="shared" ref="S3:S16" si="1">ROUND(R3*5/80, 2)</f>
-        <v>2</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" t="e">
         <f>_xlfn.IFS(Attendance!#REF!="P",5,Attendance!#REF!="O",3,Attendance!#REF!="A",0,Attendance!#REF!="N/A",0)</f>
@@ -2041,231 +2301,231 @@
       <c r="A5" t="s">
         <v>13</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="e">
         <f>_xlfn.IFS(Attendance!C4="P",5,Attendance!C4="O",3,Attendance!C4="A",0,Attendance!C4="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="C5">
+        <v>#N/A</v>
+      </c>
+      <c r="C5" t="e">
         <f>_xlfn.IFS(Attendance!D4="P",5,Attendance!D4="O",3,Attendance!D4="A",0,Attendance!D4="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="D5">
+        <v>#N/A</v>
+      </c>
+      <c r="D5" t="e">
         <f>_xlfn.IFS(Attendance!E4="P",5,Attendance!E4="O",3,Attendance!E4="A",0,Attendance!E4="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="E5">
+        <v>#N/A</v>
+      </c>
+      <c r="E5" t="e">
         <f>_xlfn.IFS(Attendance!F4="P",5,Attendance!F4="O",3,Attendance!F4="A",0,Attendance!F4="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="F5">
+        <v>#N/A</v>
+      </c>
+      <c r="F5" t="e">
         <f>_xlfn.IFS(Attendance!G4="P",5,Attendance!G4="O",3,Attendance!G4="A",0,Attendance!G4="N/A",0)</f>
-        <v>3</v>
-      </c>
-      <c r="G5">
+        <v>#N/A</v>
+      </c>
+      <c r="G5" t="e">
         <f>_xlfn.IFS(Attendance!H4="P",5,Attendance!H4="O",3,Attendance!H4="A",0,Attendance!H4="N/A",0)</f>
-        <v>3</v>
-      </c>
-      <c r="H5">
+        <v>#N/A</v>
+      </c>
+      <c r="H5" t="e">
         <f>_xlfn.IFS(Attendance!I4="P",5,Attendance!I4="O",3,Attendance!I4="A",0,Attendance!I4="N/A",0)</f>
-        <v>3</v>
-      </c>
-      <c r="I5">
+        <v>#N/A</v>
+      </c>
+      <c r="I5" t="e">
         <f>_xlfn.IFS(Attendance!J4="P",5,Attendance!J4="O",3,Attendance!J4="A",0,Attendance!J4="N/A",0)</f>
-        <v>3</v>
-      </c>
-      <c r="J5">
+        <v>#N/A</v>
+      </c>
+      <c r="J5" t="e">
         <f>_xlfn.IFS(Attendance!K4="P",5,Attendance!K4="O",3,Attendance!K4="A",0,Attendance!K4="N/A",0)</f>
-        <v>3</v>
-      </c>
-      <c r="K5">
+        <v>#N/A</v>
+      </c>
+      <c r="K5" t="e">
         <f>_xlfn.IFS(Attendance!L4="P",5,Attendance!L4="O",3,Attendance!L4="A",0,Attendance!L4="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="L5">
+        <v>#N/A</v>
+      </c>
+      <c r="L5" t="e">
         <f>_xlfn.IFS(Attendance!M4="P",5,Attendance!M4="O",3,Attendance!M4="A",0,Attendance!M4="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="M5">
+        <v>#N/A</v>
+      </c>
+      <c r="M5" t="e">
         <f>_xlfn.IFS(Attendance!N4="P",5,Attendance!N4="O",3,Attendance!N4="A",0,Attendance!N4="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="N5">
+        <v>#N/A</v>
+      </c>
+      <c r="N5" t="e">
         <f>_xlfn.IFS(Attendance!O4="P",5,Attendance!O4="O",3,Attendance!O4="A",0,Attendance!O4="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="O5">
+        <v>#N/A</v>
+      </c>
+      <c r="O5" t="e">
         <f>_xlfn.IFS(Attendance!P4="P",5,Attendance!P4="O",3,Attendance!P4="A",0,Attendance!P4="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="P5">
+        <v>#N/A</v>
+      </c>
+      <c r="P5" t="e">
         <f>_xlfn.IFS(Attendance!Q4="P",5,Attendance!Q4="O",3,Attendance!Q4="A",0,Attendance!Q4="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="Q5">
+        <v>#N/A</v>
+      </c>
+      <c r="Q5" t="e">
         <f>_xlfn.IFS(Attendance!R4="P",5,Attendance!R4="O",3,Attendance!R4="A",0,Attendance!R4="N/A",0)</f>
-        <v>3</v>
-      </c>
-      <c r="R5">
+        <v>#N/A</v>
+      </c>
+      <c r="R5" t="e">
         <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
-      <c r="S5">
+        <v>#N/A</v>
+      </c>
+      <c r="S5" t="e">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="e">
         <f>_xlfn.IFS(Attendance!C5="P",5,Attendance!C5="O",3,Attendance!C5="A",0,Attendance!C5="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="C6">
+        <v>#N/A</v>
+      </c>
+      <c r="C6" t="e">
         <f>_xlfn.IFS(Attendance!D5="P",5,Attendance!D5="O",3,Attendance!D5="A",0,Attendance!D5="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="D6">
+        <v>#N/A</v>
+      </c>
+      <c r="D6" t="e">
         <f>_xlfn.IFS(Attendance!E5="P",5,Attendance!E5="O",3,Attendance!E5="A",0,Attendance!E5="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="E6">
+        <v>#N/A</v>
+      </c>
+      <c r="E6" t="e">
         <f>_xlfn.IFS(Attendance!F5="P",5,Attendance!F5="O",3,Attendance!F5="A",0,Attendance!F5="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="F6">
+        <v>#N/A</v>
+      </c>
+      <c r="F6" t="e">
         <f>_xlfn.IFS(Attendance!G5="P",5,Attendance!G5="O",3,Attendance!G5="A",0,Attendance!G5="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="G6">
+        <v>#N/A</v>
+      </c>
+      <c r="G6" t="e">
         <f>_xlfn.IFS(Attendance!H5="P",5,Attendance!H5="O",3,Attendance!H5="A",0,Attendance!H5="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="H6">
+        <v>#N/A</v>
+      </c>
+      <c r="H6" t="e">
         <f>_xlfn.IFS(Attendance!I5="P",5,Attendance!I5="O",3,Attendance!I5="A",0,Attendance!I5="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="I6">
+        <v>#N/A</v>
+      </c>
+      <c r="I6" t="e">
         <f>_xlfn.IFS(Attendance!J5="P",5,Attendance!J5="O",3,Attendance!J5="A",0,Attendance!J5="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="J6">
+        <v>#N/A</v>
+      </c>
+      <c r="J6" t="e">
         <f>_xlfn.IFS(Attendance!K5="P",5,Attendance!K5="O",3,Attendance!K5="A",0,Attendance!K5="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="K6">
+        <v>#N/A</v>
+      </c>
+      <c r="K6" t="e">
         <f>_xlfn.IFS(Attendance!L5="P",5,Attendance!L5="O",3,Attendance!L5="A",0,Attendance!L5="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="L6">
+        <v>#N/A</v>
+      </c>
+      <c r="L6" t="e">
         <f>_xlfn.IFS(Attendance!M5="P",5,Attendance!M5="O",3,Attendance!M5="A",0,Attendance!M5="N/A",0)</f>
-        <v>3</v>
-      </c>
-      <c r="M6">
+        <v>#N/A</v>
+      </c>
+      <c r="M6" t="e">
         <f>_xlfn.IFS(Attendance!N5="P",5,Attendance!N5="O",3,Attendance!N5="A",0,Attendance!N5="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="N6">
+        <v>#N/A</v>
+      </c>
+      <c r="N6" t="e">
         <f>_xlfn.IFS(Attendance!O5="P",5,Attendance!O5="O",3,Attendance!O5="A",0,Attendance!O5="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="O6">
+        <v>#N/A</v>
+      </c>
+      <c r="O6" t="e">
         <f>_xlfn.IFS(Attendance!P5="P",5,Attendance!P5="O",3,Attendance!P5="A",0,Attendance!P5="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="P6">
+        <v>#N/A</v>
+      </c>
+      <c r="P6" t="e">
         <f>_xlfn.IFS(Attendance!Q5="P",5,Attendance!Q5="O",3,Attendance!Q5="A",0,Attendance!Q5="N/A",0)</f>
-        <v>3</v>
-      </c>
-      <c r="Q6">
+        <v>#N/A</v>
+      </c>
+      <c r="Q6" t="e">
         <f>_xlfn.IFS(Attendance!R5="P",5,Attendance!R5="O",3,Attendance!R5="A",0,Attendance!R5="N/A",0)</f>
-        <v>3</v>
-      </c>
-      <c r="R6">
+        <v>#N/A</v>
+      </c>
+      <c r="R6" t="e">
         <f t="shared" si="0"/>
-        <v>64</v>
-      </c>
-      <c r="S6">
+        <v>#N/A</v>
+      </c>
+      <c r="S6" t="e">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="e">
         <f>_xlfn.IFS(Attendance!C6="P",5,Attendance!C6="O",3,Attendance!C6="A",0,Attendance!C6="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="C7">
+        <v>#N/A</v>
+      </c>
+      <c r="C7" t="e">
         <f>_xlfn.IFS(Attendance!D6="P",5,Attendance!D6="O",3,Attendance!D6="A",0,Attendance!D6="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="D7">
+        <v>#N/A</v>
+      </c>
+      <c r="D7" t="e">
         <f>_xlfn.IFS(Attendance!E6="P",5,Attendance!E6="O",3,Attendance!E6="A",0,Attendance!E6="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="E7">
+        <v>#N/A</v>
+      </c>
+      <c r="E7" t="e">
         <f>_xlfn.IFS(Attendance!F6="P",5,Attendance!F6="O",3,Attendance!F6="A",0,Attendance!F6="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="F7">
+        <v>#N/A</v>
+      </c>
+      <c r="F7" t="e">
         <f>_xlfn.IFS(Attendance!G6="P",5,Attendance!G6="O",3,Attendance!G6="A",0,Attendance!G6="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="G7">
+        <v>#N/A</v>
+      </c>
+      <c r="G7" t="e">
         <f>_xlfn.IFS(Attendance!H6="P",5,Attendance!H6="O",3,Attendance!H6="A",0,Attendance!H6="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="H7">
+        <v>#N/A</v>
+      </c>
+      <c r="H7" t="e">
         <f>_xlfn.IFS(Attendance!I6="P",5,Attendance!I6="O",3,Attendance!I6="A",0,Attendance!I6="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="I7">
+        <v>#N/A</v>
+      </c>
+      <c r="I7" t="e">
         <f>_xlfn.IFS(Attendance!J6="P",5,Attendance!J6="O",3,Attendance!J6="A",0,Attendance!J6="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="J7">
+        <v>#N/A</v>
+      </c>
+      <c r="J7" t="e">
         <f>_xlfn.IFS(Attendance!K6="P",5,Attendance!K6="O",3,Attendance!K6="A",0,Attendance!K6="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="K7">
+        <v>#N/A</v>
+      </c>
+      <c r="K7" t="e">
         <f>_xlfn.IFS(Attendance!L6="P",5,Attendance!L6="O",3,Attendance!L6="A",0,Attendance!L6="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="L7">
+        <v>#N/A</v>
+      </c>
+      <c r="L7" t="e">
         <f>_xlfn.IFS(Attendance!M6="P",5,Attendance!M6="O",3,Attendance!M6="A",0,Attendance!M6="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="M7">
+        <v>#N/A</v>
+      </c>
+      <c r="M7" t="e">
         <f>_xlfn.IFS(Attendance!N6="P",5,Attendance!N6="O",3,Attendance!N6="A",0,Attendance!N6="N/A",0)</f>
-        <v>3</v>
-      </c>
-      <c r="N7">
+        <v>#N/A</v>
+      </c>
+      <c r="N7" t="e">
         <f>_xlfn.IFS(Attendance!O6="P",5,Attendance!O6="O",3,Attendance!O6="A",0,Attendance!O6="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="O7">
+        <v>#N/A</v>
+      </c>
+      <c r="O7" t="e">
         <f>_xlfn.IFS(Attendance!P6="P",5,Attendance!P6="O",3,Attendance!P6="A",0,Attendance!P6="N/A",0)</f>
-        <v>3</v>
-      </c>
-      <c r="P7">
+        <v>#N/A</v>
+      </c>
+      <c r="P7" t="e">
         <f>_xlfn.IFS(Attendance!Q6="P",5,Attendance!Q6="O",3,Attendance!Q6="A",0,Attendance!Q6="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="Q7">
+        <v>#N/A</v>
+      </c>
+      <c r="Q7" t="e">
         <f>_xlfn.IFS(Attendance!R6="P",5,Attendance!R6="O",3,Attendance!R6="A",0,Attendance!R6="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="R7">
+        <v>#N/A</v>
+      </c>
+      <c r="R7" t="e">
         <f t="shared" si="0"/>
-        <v>61</v>
-      </c>
-      <c r="S7">
+        <v>#N/A</v>
+      </c>
+      <c r="S7" t="e">
         <f t="shared" si="1"/>
-        <v>3.81</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
@@ -2274,7 +2534,7 @@
       </c>
       <c r="B8">
         <f>_xlfn.IFS(Attendance!C7="P",5,Attendance!C7="O",3,Attendance!C7="A",0,Attendance!C7="N/A",0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C8">
         <f>_xlfn.IFS(Attendance!D7="P",5,Attendance!D7="O",3,Attendance!D7="A",0,Attendance!D7="N/A",0)</f>
@@ -2282,39 +2542,39 @@
       </c>
       <c r="D8">
         <f>_xlfn.IFS(Attendance!E7="P",5,Attendance!E7="O",3,Attendance!E7="A",0,Attendance!E7="N/A",0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <f>_xlfn.IFS(Attendance!F7="P",5,Attendance!F7="O",3,Attendance!F7="A",0,Attendance!F7="N/A",0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <f>_xlfn.IFS(Attendance!G7="P",5,Attendance!G7="O",3,Attendance!G7="A",0,Attendance!G7="N/A",0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <f>_xlfn.IFS(Attendance!H7="P",5,Attendance!H7="O",3,Attendance!H7="A",0,Attendance!H7="N/A",0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <f>_xlfn.IFS(Attendance!I7="P",5,Attendance!I7="O",3,Attendance!I7="A",0,Attendance!I7="N/A",0)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I8">
         <f>_xlfn.IFS(Attendance!J7="P",5,Attendance!J7="O",3,Attendance!J7="A",0,Attendance!J7="N/A",0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <f>_xlfn.IFS(Attendance!K7="P",5,Attendance!K7="O",3,Attendance!K7="A",0,Attendance!K7="N/A",0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K8">
         <f>_xlfn.IFS(Attendance!L7="P",5,Attendance!L7="O",3,Attendance!L7="A",0,Attendance!L7="N/A",0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L8">
         <f>_xlfn.IFS(Attendance!M7="P",5,Attendance!M7="O",3,Attendance!M7="A",0,Attendance!M7="N/A",0)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M8">
         <f>_xlfn.IFS(Attendance!N7="P",5,Attendance!N7="O",3,Attendance!N7="A",0,Attendance!N7="N/A",0)</f>
@@ -2322,27 +2582,27 @@
       </c>
       <c r="N8">
         <f>_xlfn.IFS(Attendance!O7="P",5,Attendance!O7="O",3,Attendance!O7="A",0,Attendance!O7="N/A",0)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O8">
         <f>_xlfn.IFS(Attendance!P7="P",5,Attendance!P7="O",3,Attendance!P7="A",0,Attendance!P7="N/A",0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P8">
         <f>_xlfn.IFS(Attendance!Q7="P",5,Attendance!Q7="O",3,Attendance!Q7="A",0,Attendance!Q7="N/A",0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q8">
         <f>_xlfn.IFS(Attendance!R7="P",5,Attendance!R7="O",3,Attendance!R7="A",0,Attendance!R7="N/A",0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R8">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="S8">
         <f t="shared" si="1"/>
-        <v>2.56</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
@@ -2359,11 +2619,11 @@
       </c>
       <c r="D9">
         <f>_xlfn.IFS(Attendance!E8="P",5,Attendance!E8="O",3,Attendance!E8="A",0,Attendance!E8="N/A",0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <f>_xlfn.IFS(Attendance!F8="P",5,Attendance!F8="O",3,Attendance!F8="A",0,Attendance!F8="N/A",0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F9">
         <f>_xlfn.IFS(Attendance!G8="P",5,Attendance!G8="O",3,Attendance!G8="A",0,Attendance!G8="N/A",0)</f>
@@ -2383,43 +2643,43 @@
       </c>
       <c r="J9">
         <f>_xlfn.IFS(Attendance!K8="P",5,Attendance!K8="O",3,Attendance!K8="A",0,Attendance!K8="N/A",0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K9">
         <f>_xlfn.IFS(Attendance!L8="P",5,Attendance!L8="O",3,Attendance!L8="A",0,Attendance!L8="N/A",0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L9">
         <f>_xlfn.IFS(Attendance!M8="P",5,Attendance!M8="O",3,Attendance!M8="A",0,Attendance!M8="N/A",0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M9">
         <f>_xlfn.IFS(Attendance!N8="P",5,Attendance!N8="O",3,Attendance!N8="A",0,Attendance!N8="N/A",0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N9">
         <f>_xlfn.IFS(Attendance!O8="P",5,Attendance!O8="O",3,Attendance!O8="A",0,Attendance!O8="N/A",0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O9">
         <f>_xlfn.IFS(Attendance!P8="P",5,Attendance!P8="O",3,Attendance!P8="A",0,Attendance!P8="N/A",0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P9">
         <f>_xlfn.IFS(Attendance!Q8="P",5,Attendance!Q8="O",3,Attendance!Q8="A",0,Attendance!Q8="N/A",0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q9">
         <f>_xlfn.IFS(Attendance!R8="P",5,Attendance!R8="O",3,Attendance!R8="A",0,Attendance!R8="N/A",0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R9">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="S9">
         <f t="shared" si="1"/>
-        <v>0.38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
@@ -2444,23 +2704,23 @@
       </c>
       <c r="F10">
         <f>_xlfn.IFS(Attendance!G9="P",5,Attendance!G9="O",3,Attendance!G9="A",0,Attendance!G9="N/A",0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G10">
         <f>_xlfn.IFS(Attendance!H9="P",5,Attendance!H9="O",3,Attendance!H9="A",0,Attendance!H9="N/A",0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10">
         <f>_xlfn.IFS(Attendance!I9="P",5,Attendance!I9="O",3,Attendance!I9="A",0,Attendance!I9="N/A",0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I10">
         <f>_xlfn.IFS(Attendance!J9="P",5,Attendance!J9="O",3,Attendance!J9="A",0,Attendance!J9="N/A",0)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J10">
         <f>_xlfn.IFS(Attendance!K9="P",5,Attendance!K9="O",3,Attendance!K9="A",0,Attendance!K9="N/A",0)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K10">
         <f>_xlfn.IFS(Attendance!L9="P",5,Attendance!L9="O",3,Attendance!L9="A",0,Attendance!L9="N/A",0)</f>
@@ -2476,27 +2736,27 @@
       </c>
       <c r="N10">
         <f>_xlfn.IFS(Attendance!O9="P",5,Attendance!O9="O",3,Attendance!O9="A",0,Attendance!O9="N/A",0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O10">
         <f>_xlfn.IFS(Attendance!P9="P",5,Attendance!P9="O",3,Attendance!P9="A",0,Attendance!P9="N/A",0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P10">
         <f>_xlfn.IFS(Attendance!Q9="P",5,Attendance!Q9="O",3,Attendance!Q9="A",0,Attendance!Q9="N/A",0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q10">
         <f>_xlfn.IFS(Attendance!R9="P",5,Attendance!R9="O",3,Attendance!R9="A",0,Attendance!R9="N/A",0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R10">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="S10">
         <f t="shared" si="1"/>
-        <v>1.56</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
@@ -2580,77 +2840,77 @@
       <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="e">
         <f>_xlfn.IFS(Attendance!C10="P",5,Attendance!C10="O",3,Attendance!C10="A",0,Attendance!C10="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="C12">
+        <v>#N/A</v>
+      </c>
+      <c r="C12" t="e">
         <f>_xlfn.IFS(Attendance!D10="P",5,Attendance!D10="O",3,Attendance!D10="A",0,Attendance!D10="N/A",0)</f>
-        <v>3</v>
-      </c>
-      <c r="D12">
+        <v>#N/A</v>
+      </c>
+      <c r="D12" t="e">
         <f>_xlfn.IFS(Attendance!E10="P",5,Attendance!E10="O",3,Attendance!E10="A",0,Attendance!E10="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="E12">
+        <v>#N/A</v>
+      </c>
+      <c r="E12" t="e">
         <f>_xlfn.IFS(Attendance!F10="P",5,Attendance!F10="O",3,Attendance!F10="A",0,Attendance!F10="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="F12">
+        <v>#N/A</v>
+      </c>
+      <c r="F12" t="e">
         <f>_xlfn.IFS(Attendance!G10="P",5,Attendance!G10="O",3,Attendance!G10="A",0,Attendance!G10="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="G12">
+        <v>#N/A</v>
+      </c>
+      <c r="G12" t="e">
         <f>_xlfn.IFS(Attendance!H10="P",5,Attendance!H10="O",3,Attendance!H10="A",0,Attendance!H10="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="H12">
+        <v>#N/A</v>
+      </c>
+      <c r="H12" t="e">
         <f>_xlfn.IFS(Attendance!I10="P",5,Attendance!I10="O",3,Attendance!I10="A",0,Attendance!I10="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="I12">
+        <v>#N/A</v>
+      </c>
+      <c r="I12" t="e">
         <f>_xlfn.IFS(Attendance!J10="P",5,Attendance!J10="O",3,Attendance!J10="A",0,Attendance!J10="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="J12">
+        <v>#N/A</v>
+      </c>
+      <c r="J12" t="e">
         <f>_xlfn.IFS(Attendance!K10="P",5,Attendance!K10="O",3,Attendance!K10="A",0,Attendance!K10="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="K12">
+        <v>#N/A</v>
+      </c>
+      <c r="K12" t="e">
         <f>_xlfn.IFS(Attendance!L10="P",5,Attendance!L10="O",3,Attendance!L10="A",0,Attendance!L10="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="L12">
+        <v>#N/A</v>
+      </c>
+      <c r="L12" t="e">
         <f>_xlfn.IFS(Attendance!M10="P",5,Attendance!M10="O",3,Attendance!M10="A",0,Attendance!M10="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="M12">
+        <v>#N/A</v>
+      </c>
+      <c r="M12" t="e">
         <f>_xlfn.IFS(Attendance!N10="P",5,Attendance!N10="O",3,Attendance!N10="A",0,Attendance!N10="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="N12">
+        <v>#N/A</v>
+      </c>
+      <c r="N12" t="e">
         <f>_xlfn.IFS(Attendance!O10="P",5,Attendance!O10="O",3,Attendance!O10="A",0,Attendance!O10="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="O12">
+        <v>#N/A</v>
+      </c>
+      <c r="O12" t="e">
         <f>_xlfn.IFS(Attendance!P10="P",5,Attendance!P10="O",3,Attendance!P10="A",0,Attendance!P10="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="P12">
+        <v>#N/A</v>
+      </c>
+      <c r="P12" t="e">
         <f>_xlfn.IFS(Attendance!Q10="P",5,Attendance!Q10="O",3,Attendance!Q10="A",0,Attendance!Q10="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q12">
+        <v>#N/A</v>
+      </c>
+      <c r="Q12" t="e">
         <f>_xlfn.IFS(Attendance!R10="P",5,Attendance!R10="O",3,Attendance!R10="A",0,Attendance!R10="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="R12">
+        <v>#N/A</v>
+      </c>
+      <c r="R12" t="e">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="S12">
+        <v>#N/A</v>
+      </c>
+      <c r="S12" t="e">
         <f t="shared" si="1"/>
-        <v>1.1299999999999999</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
@@ -2659,15 +2919,15 @@
       </c>
       <c r="B13">
         <f>_xlfn.IFS(Attendance!C11="P",5,Attendance!C11="O",3,Attendance!C11="A",0,Attendance!C11="N/A",0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C13">
         <f>_xlfn.IFS(Attendance!D11="P",5,Attendance!D11="O",3,Attendance!D11="A",0,Attendance!D11="N/A",0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <f>_xlfn.IFS(Attendance!E11="P",5,Attendance!E11="O",3,Attendance!E11="A",0,Attendance!E11="N/A",0)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E13">
         <f>_xlfn.IFS(Attendance!F11="P",5,Attendance!F11="O",3,Attendance!F11="A",0,Attendance!F11="N/A",0)</f>
@@ -2675,136 +2935,136 @@
       </c>
       <c r="F13">
         <f>_xlfn.IFS(Attendance!G11="P",5,Attendance!G11="O",3,Attendance!G11="A",0,Attendance!G11="N/A",0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G13">
         <f>_xlfn.IFS(Attendance!H11="P",5,Attendance!H11="O",3,Attendance!H11="A",0,Attendance!H11="N/A",0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H13">
         <f>_xlfn.IFS(Attendance!I11="P",5,Attendance!I11="O",3,Attendance!I11="A",0,Attendance!I11="N/A",0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I13">
         <f>_xlfn.IFS(Attendance!J11="P",5,Attendance!J11="O",3,Attendance!J11="A",0,Attendance!J11="N/A",0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J13">
         <f>_xlfn.IFS(Attendance!K11="P",5,Attendance!K11="O",3,Attendance!K11="A",0,Attendance!K11="N/A",0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K13">
         <f>_xlfn.IFS(Attendance!L11="P",5,Attendance!L11="O",3,Attendance!L11="A",0,Attendance!L11="N/A",0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L13">
         <f>_xlfn.IFS(Attendance!M11="P",5,Attendance!M11="O",3,Attendance!M11="A",0,Attendance!M11="N/A",0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M13">
         <f>_xlfn.IFS(Attendance!N11="P",5,Attendance!N11="O",3,Attendance!N11="A",0,Attendance!N11="N/A",0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <f>_xlfn.IFS(Attendance!O11="P",5,Attendance!O11="O",3,Attendance!O11="A",0,Attendance!O11="N/A",0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O13">
         <f>_xlfn.IFS(Attendance!P11="P",5,Attendance!P11="O",3,Attendance!P11="A",0,Attendance!P11="N/A",0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P13">
         <f>_xlfn.IFS(Attendance!Q11="P",5,Attendance!Q11="O",3,Attendance!Q11="A",0,Attendance!Q11="N/A",0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q13">
         <f>_xlfn.IFS(Attendance!R11="P",5,Attendance!R11="O",3,Attendance!R11="A",0,Attendance!R11="N/A",0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R13">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="S13">
         <f t="shared" si="1"/>
-        <v>0.38</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>6</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="e">
         <f>_xlfn.IFS(Attendance!C12="P",5,Attendance!C12="O",3,Attendance!C12="A",0,Attendance!C12="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="C14">
+        <v>#N/A</v>
+      </c>
+      <c r="C14" t="e">
         <f>_xlfn.IFS(Attendance!D12="P",5,Attendance!D12="O",3,Attendance!D12="A",0,Attendance!D12="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="D14">
+        <v>#N/A</v>
+      </c>
+      <c r="D14" t="e">
         <f>_xlfn.IFS(Attendance!E12="P",5,Attendance!E12="O",3,Attendance!E12="A",0,Attendance!E12="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="E14">
+        <v>#N/A</v>
+      </c>
+      <c r="E14" t="e">
         <f>_xlfn.IFS(Attendance!F12="P",5,Attendance!F12="O",3,Attendance!F12="A",0,Attendance!F12="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="F14">
+        <v>#N/A</v>
+      </c>
+      <c r="F14" t="e">
         <f>_xlfn.IFS(Attendance!G12="P",5,Attendance!G12="O",3,Attendance!G12="A",0,Attendance!G12="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="G14">
+        <v>#N/A</v>
+      </c>
+      <c r="G14" t="e">
         <f>_xlfn.IFS(Attendance!H12="P",5,Attendance!H12="O",3,Attendance!H12="A",0,Attendance!H12="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="H14">
+        <v>#N/A</v>
+      </c>
+      <c r="H14" t="e">
         <f>_xlfn.IFS(Attendance!I12="P",5,Attendance!I12="O",3,Attendance!I12="A",0,Attendance!I12="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="I14">
+        <v>#N/A</v>
+      </c>
+      <c r="I14" t="e">
         <f>_xlfn.IFS(Attendance!J12="P",5,Attendance!J12="O",3,Attendance!J12="A",0,Attendance!J12="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="J14">
+        <v>#N/A</v>
+      </c>
+      <c r="J14" t="e">
         <f>_xlfn.IFS(Attendance!K12="P",5,Attendance!K12="O",3,Attendance!K12="A",0,Attendance!K12="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="K14">
+        <v>#N/A</v>
+      </c>
+      <c r="K14" t="e">
         <f>_xlfn.IFS(Attendance!L12="P",5,Attendance!L12="O",3,Attendance!L12="A",0,Attendance!L12="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="L14">
+        <v>#N/A</v>
+      </c>
+      <c r="L14" t="e">
         <f>_xlfn.IFS(Attendance!M12="P",5,Attendance!M12="O",3,Attendance!M12="A",0,Attendance!M12="N/A",0)</f>
-        <v>3</v>
-      </c>
-      <c r="M14">
+        <v>#N/A</v>
+      </c>
+      <c r="M14" t="e">
         <f>_xlfn.IFS(Attendance!N12="P",5,Attendance!N12="O",3,Attendance!N12="A",0,Attendance!N12="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="N14">
+        <v>#N/A</v>
+      </c>
+      <c r="N14" t="e">
         <f>_xlfn.IFS(Attendance!O12="P",5,Attendance!O12="O",3,Attendance!O12="A",0,Attendance!O12="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="O14">
+        <v>#N/A</v>
+      </c>
+      <c r="O14" t="e">
         <f>_xlfn.IFS(Attendance!P12="P",5,Attendance!P12="O",3,Attendance!P12="A",0,Attendance!P12="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="P14">
+        <v>#N/A</v>
+      </c>
+      <c r="P14" t="e">
         <f>_xlfn.IFS(Attendance!Q12="P",5,Attendance!Q12="O",3,Attendance!Q12="A",0,Attendance!Q12="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q14">
+        <v>#N/A</v>
+      </c>
+      <c r="Q14" t="e">
         <f>_xlfn.IFS(Attendance!R12="P",5,Attendance!R12="O",3,Attendance!R12="A",0,Attendance!R12="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="R14">
+        <v>#N/A</v>
+      </c>
+      <c r="R14" t="e">
         <f t="shared" si="0"/>
-        <v>43</v>
-      </c>
-      <c r="S14">
+        <v>#N/A</v>
+      </c>
+      <c r="S14" t="e">
         <f t="shared" si="1"/>
-        <v>2.69</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
@@ -2813,7 +3073,7 @@
       </c>
       <c r="B15">
         <f>_xlfn.IFS(Attendance!C13="P",5,Attendance!C13="O",3,Attendance!C13="A",0,Attendance!C13="N/A",0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C15">
         <f>_xlfn.IFS(Attendance!D13="P",5,Attendance!D13="O",3,Attendance!D13="A",0,Attendance!D13="N/A",0)</f>
@@ -2829,68 +3089,68 @@
       </c>
       <c r="F15">
         <f>_xlfn.IFS(Attendance!G13="P",5,Attendance!G13="O",3,Attendance!G13="A",0,Attendance!G13="N/A",0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G15">
         <f>_xlfn.IFS(Attendance!H13="P",5,Attendance!H13="O",3,Attendance!H13="A",0,Attendance!H13="N/A",0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H15">
         <f>_xlfn.IFS(Attendance!I13="P",5,Attendance!I13="O",3,Attendance!I13="A",0,Attendance!I13="N/A",0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I15">
         <f>_xlfn.IFS(Attendance!J13="P",5,Attendance!J13="O",3,Attendance!J13="A",0,Attendance!J13="N/A",0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J15">
         <f>_xlfn.IFS(Attendance!K13="P",5,Attendance!K13="O",3,Attendance!K13="A",0,Attendance!K13="N/A",0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K15">
         <f>_xlfn.IFS(Attendance!L13="P",5,Attendance!L13="O",3,Attendance!L13="A",0,Attendance!L13="N/A",0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L15">
         <f>_xlfn.IFS(Attendance!M13="P",5,Attendance!M13="O",3,Attendance!M13="A",0,Attendance!M13="N/A",0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M15">
         <f>_xlfn.IFS(Attendance!N13="P",5,Attendance!N13="O",3,Attendance!N13="A",0,Attendance!N13="N/A",0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N15">
         <f>_xlfn.IFS(Attendance!O13="P",5,Attendance!O13="O",3,Attendance!O13="A",0,Attendance!O13="N/A",0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O15">
         <f>_xlfn.IFS(Attendance!P13="P",5,Attendance!P13="O",3,Attendance!P13="A",0,Attendance!P13="N/A",0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P15">
         <f>_xlfn.IFS(Attendance!Q13="P",5,Attendance!Q13="O",3,Attendance!Q13="A",0,Attendance!Q13="N/A",0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q15">
         <f>_xlfn.IFS(Attendance!R13="P",5,Attendance!R13="O",3,Attendance!R13="A",0,Attendance!R13="N/A",0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="S15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16">
         <f>_xlfn.IFS(Attendance!C14="P",5,Attendance!C14="O",3,Attendance!C14="A",0,Attendance!C14="N/A",0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C16">
         <f>_xlfn.IFS(Attendance!D14="P",5,Attendance!D14="O",3,Attendance!D14="A",0,Attendance!D14="N/A",0)</f>
@@ -2898,47 +3158,47 @@
       </c>
       <c r="D16">
         <f>_xlfn.IFS(Attendance!E14="P",5,Attendance!E14="O",3,Attendance!E14="A",0,Attendance!E14="N/A",0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E16">
         <f>_xlfn.IFS(Attendance!F14="P",5,Attendance!F14="O",3,Attendance!F14="A",0,Attendance!F14="N/A",0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F16">
         <f>_xlfn.IFS(Attendance!G14="P",5,Attendance!G14="O",3,Attendance!G14="A",0,Attendance!G14="N/A",0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G16">
         <f>_xlfn.IFS(Attendance!H14="P",5,Attendance!H14="O",3,Attendance!H14="A",0,Attendance!H14="N/A",0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H16">
         <f>_xlfn.IFS(Attendance!I14="P",5,Attendance!I14="O",3,Attendance!I14="A",0,Attendance!I14="N/A",0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I16">
         <f>_xlfn.IFS(Attendance!J14="P",5,Attendance!J14="O",3,Attendance!J14="A",0,Attendance!J14="N/A",0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J16">
         <f>_xlfn.IFS(Attendance!K14="P",5,Attendance!K14="O",3,Attendance!K14="A",0,Attendance!K14="N/A",0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K16">
         <f>_xlfn.IFS(Attendance!L14="P",5,Attendance!L14="O",3,Attendance!L14="A",0,Attendance!L14="N/A",0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L16">
         <f>_xlfn.IFS(Attendance!M14="P",5,Attendance!M14="O",3,Attendance!M14="A",0,Attendance!M14="N/A",0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M16">
         <f>_xlfn.IFS(Attendance!N14="P",5,Attendance!N14="O",3,Attendance!N14="A",0,Attendance!N14="N/A",0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N16">
         <f>_xlfn.IFS(Attendance!O14="P",5,Attendance!O14="O",3,Attendance!O14="A",0,Attendance!O14="N/A",0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O16">
         <f>_xlfn.IFS(Attendance!P14="P",5,Attendance!P14="O",3,Attendance!P14="A",0,Attendance!P14="N/A",0)</f>
@@ -2950,15 +3210,15 @@
       </c>
       <c r="Q16">
         <f>_xlfn.IFS(Attendance!R14="P",5,Attendance!R14="O",3,Attendance!R14="A",0,Attendance!R14="N/A",0)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R16">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="S16">
         <f t="shared" si="1"/>
-        <v>0.31</v>
+        <v>2.56</v>
       </c>
     </row>
   </sheetData>
